--- a/SpaceDebris_site_1000/2024-095E_KZ-11-3_Kuaizhou-11.xlsx
+++ b/SpaceDebris_site_1000/2024-095E_KZ-11-3_Kuaizhou-11.xlsx
@@ -452,7002 +452,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39.09</v>
+        <v>0.25</v>
       </c>
       <c r="B2" t="n">
-        <v>23784</v>
+        <v>36571</v>
       </c>
       <c r="C2" t="n">
-        <v>38.14</v>
+        <v>1.52</v>
       </c>
       <c r="D2" t="n">
-        <v>15617</v>
+        <v>22858</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114.8</v>
+        <v>0.42</v>
       </c>
       <c r="B3" t="n">
-        <v>23669</v>
+        <v>37287</v>
       </c>
       <c r="C3" t="n">
-        <v>116.33</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>10187</v>
+        <v>20174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95.89</v>
+        <v>0.43</v>
       </c>
       <c r="B4" t="n">
-        <v>33013</v>
+        <v>37592</v>
       </c>
       <c r="C4" t="n">
-        <v>97.37</v>
+        <v>0.16</v>
       </c>
       <c r="D4" t="n">
-        <v>14799</v>
+        <v>19580</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112.75</v>
+        <v>0.89</v>
       </c>
       <c r="B5" t="n">
-        <v>26086</v>
+        <v>38034</v>
       </c>
       <c r="C5" t="n">
-        <v>111.17</v>
+        <v>7.21</v>
       </c>
       <c r="D5" t="n">
-        <v>23858</v>
+        <v>27686</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104.02</v>
+        <v>1.08</v>
       </c>
       <c r="B6" t="n">
-        <v>47371</v>
+        <v>35323</v>
       </c>
       <c r="C6" t="n">
-        <v>106.08</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>24500</v>
+        <v>28119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106.3</v>
+        <v>1.11</v>
       </c>
       <c r="B7" t="n">
-        <v>43882</v>
+        <v>36876</v>
       </c>
       <c r="C7" t="n">
-        <v>108.38</v>
+        <v>0.23</v>
       </c>
       <c r="D7" t="n">
-        <v>10758</v>
+        <v>11599</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91.03</v>
+        <v>1.18</v>
       </c>
       <c r="B8" t="n">
-        <v>23519</v>
+        <v>37351</v>
       </c>
       <c r="C8" t="n">
-        <v>92.34</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>15225</v>
+        <v>10557</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95.97</v>
+        <v>1.29</v>
       </c>
       <c r="B9" t="n">
-        <v>39372</v>
+        <v>36193</v>
       </c>
       <c r="C9" t="n">
-        <v>95.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>22042</v>
+        <v>21550</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>90.38</v>
+        <v>1.67</v>
       </c>
       <c r="B10" t="n">
-        <v>21975</v>
+        <v>36511</v>
       </c>
       <c r="C10" t="n">
-        <v>89.75</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>20312</v>
+        <v>10963</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108.66</v>
+        <v>2.37</v>
       </c>
       <c r="B11" t="n">
-        <v>39508</v>
+        <v>35362</v>
       </c>
       <c r="C11" t="n">
-        <v>104.6</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>29755</v>
+        <v>13924</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105.46</v>
+        <v>2.55</v>
       </c>
       <c r="B12" t="n">
-        <v>44971</v>
+        <v>36840</v>
       </c>
       <c r="C12" t="n">
-        <v>101.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>25898</v>
+        <v>24661</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94.38</v>
+        <v>2.64</v>
       </c>
       <c r="B13" t="n">
-        <v>33050</v>
+        <v>36907</v>
       </c>
       <c r="C13" t="n">
-        <v>93.14</v>
+        <v>8.91</v>
       </c>
       <c r="D13" t="n">
-        <v>17506</v>
+        <v>27841</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105.31</v>
+        <v>2.68</v>
       </c>
       <c r="B14" t="n">
-        <v>45018</v>
+        <v>35677</v>
       </c>
       <c r="C14" t="n">
-        <v>102.15</v>
+        <v>4.29</v>
       </c>
       <c r="D14" t="n">
-        <v>13935</v>
+        <v>28182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>98.98999999999999</v>
+        <v>2.72</v>
       </c>
       <c r="B15" t="n">
-        <v>41658</v>
+        <v>36421</v>
       </c>
       <c r="C15" t="n">
-        <v>100.09</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>10397</v>
+        <v>27486</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101.56</v>
+        <v>2.85</v>
       </c>
       <c r="B16" t="n">
-        <v>47288</v>
+        <v>36345</v>
       </c>
       <c r="C16" t="n">
-        <v>101.5</v>
+        <v>8.44</v>
       </c>
       <c r="D16" t="n">
-        <v>28327</v>
+        <v>10449</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105.72</v>
+        <v>3.08</v>
       </c>
       <c r="B17" t="n">
-        <v>44174</v>
+        <v>37452</v>
       </c>
       <c r="C17" t="n">
-        <v>104.77</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>15929</v>
+        <v>27905</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105.72</v>
+        <v>3.57</v>
       </c>
       <c r="B18" t="n">
-        <v>43854</v>
+        <v>34837</v>
       </c>
       <c r="C18" t="n">
-        <v>105.91</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>20778</v>
+        <v>24365</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103.83</v>
+        <v>4.2</v>
       </c>
       <c r="B19" t="n">
-        <v>49487</v>
+        <v>35678</v>
       </c>
       <c r="C19" t="n">
-        <v>100.41</v>
+        <v>5.23</v>
       </c>
       <c r="D19" t="n">
-        <v>20064</v>
+        <v>20805</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101.27</v>
+        <v>5.15</v>
       </c>
       <c r="B20" t="n">
-        <v>49824</v>
+        <v>35550</v>
       </c>
       <c r="C20" t="n">
-        <v>100.22</v>
+        <v>11.86</v>
       </c>
       <c r="D20" t="n">
-        <v>13484</v>
+        <v>24942</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121.51</v>
+        <v>5.16</v>
       </c>
       <c r="B21" t="n">
-        <v>22888</v>
+        <v>33075</v>
       </c>
       <c r="C21" t="n">
-        <v>122.17</v>
+        <v>10.98</v>
       </c>
       <c r="D21" t="n">
-        <v>26601</v>
+        <v>18545</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97.73999999999999</v>
+        <v>5.18</v>
       </c>
       <c r="B22" t="n">
-        <v>40421</v>
+        <v>34911</v>
       </c>
       <c r="C22" t="n">
-        <v>99.75</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>17414</v>
+        <v>15343</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>101.56</v>
+        <v>5.31</v>
       </c>
       <c r="B23" t="n">
-        <v>44523</v>
+        <v>34158</v>
       </c>
       <c r="C23" t="n">
-        <v>101.77</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>10007</v>
+        <v>28168</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105.05</v>
+        <v>6.25</v>
       </c>
       <c r="B24" t="n">
-        <v>46383</v>
+        <v>33667</v>
       </c>
       <c r="C24" t="n">
-        <v>102.15</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>17411</v>
+        <v>10548</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>91.16</v>
+        <v>6.26</v>
       </c>
       <c r="B25" t="n">
-        <v>22279</v>
+        <v>33822</v>
       </c>
       <c r="C25" t="n">
-        <v>89.15000000000001</v>
+        <v>17</v>
       </c>
       <c r="D25" t="n">
-        <v>26993</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103.55</v>
+        <v>6.45</v>
       </c>
       <c r="B26" t="n">
-        <v>47464</v>
+        <v>32605</v>
       </c>
       <c r="C26" t="n">
-        <v>105.79</v>
+        <v>2.82</v>
       </c>
       <c r="D26" t="n">
-        <v>15944</v>
+        <v>13971</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10.2</v>
+        <v>7.05</v>
       </c>
       <c r="B27" t="n">
-        <v>25039</v>
+        <v>32269</v>
       </c>
       <c r="C27" t="n">
-        <v>9.56</v>
+        <v>7.04</v>
       </c>
       <c r="D27" t="n">
-        <v>16475</v>
+        <v>26886</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105.89</v>
+        <v>7.06</v>
       </c>
       <c r="B28" t="n">
-        <v>46195</v>
+        <v>34571</v>
       </c>
       <c r="C28" t="n">
-        <v>108.65</v>
+        <v>3.73</v>
       </c>
       <c r="D28" t="n">
-        <v>17502</v>
+        <v>23975</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113.06</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="B29" t="n">
-        <v>24238</v>
+        <v>31883</v>
       </c>
       <c r="C29" t="n">
-        <v>115.87</v>
+        <v>7.94</v>
       </c>
       <c r="D29" t="n">
-        <v>21932</v>
+        <v>26527</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>90.06</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="B30" t="n">
-        <v>22464</v>
+        <v>32395</v>
       </c>
       <c r="C30" t="n">
-        <v>89.2</v>
+        <v>12.56</v>
       </c>
       <c r="D30" t="n">
-        <v>16758</v>
+        <v>28695</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>90.65000000000001</v>
+        <v>10.53</v>
       </c>
       <c r="B31" t="n">
-        <v>25998</v>
+        <v>30973</v>
       </c>
       <c r="C31" t="n">
-        <v>92.69</v>
+        <v>10.1</v>
       </c>
       <c r="D31" t="n">
-        <v>28973</v>
+        <v>28081</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>48.38</v>
+        <v>11.23</v>
       </c>
       <c r="B32" t="n">
-        <v>22558</v>
+        <v>30029</v>
       </c>
       <c r="C32" t="n">
-        <v>49.07</v>
+        <v>8.25</v>
       </c>
       <c r="D32" t="n">
-        <v>15817</v>
+        <v>15249</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>99.63</v>
+        <v>11.3</v>
       </c>
       <c r="B33" t="n">
-        <v>44272</v>
+        <v>31189</v>
       </c>
       <c r="C33" t="n">
-        <v>100.06</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>17666</v>
+        <v>18629</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>100.5</v>
+        <v>11.53</v>
       </c>
       <c r="B34" t="n">
-        <v>45840</v>
+        <v>30209</v>
       </c>
       <c r="C34" t="n">
-        <v>96.04000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="D34" t="n">
-        <v>12291</v>
+        <v>12655</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109.3</v>
+        <v>11.81</v>
       </c>
       <c r="B35" t="n">
-        <v>33213</v>
+        <v>28590</v>
       </c>
       <c r="C35" t="n">
-        <v>112.28</v>
+        <v>8.99</v>
       </c>
       <c r="D35" t="n">
-        <v>13406</v>
+        <v>16243</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>97.17</v>
+        <v>12.22</v>
       </c>
       <c r="B36" t="n">
-        <v>40504</v>
+        <v>29621</v>
       </c>
       <c r="C36" t="n">
-        <v>97.3</v>
+        <v>9.5</v>
       </c>
       <c r="D36" t="n">
-        <v>11149</v>
+        <v>25497</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>100.18</v>
+        <v>12.48</v>
       </c>
       <c r="B37" t="n">
-        <v>44909</v>
+        <v>30246</v>
       </c>
       <c r="C37" t="n">
-        <v>101.02</v>
+        <v>10.29</v>
       </c>
       <c r="D37" t="n">
-        <v>21626</v>
+        <v>21043</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>98.27</v>
+        <v>12.54</v>
       </c>
       <c r="B38" t="n">
-        <v>42722</v>
+        <v>26676</v>
       </c>
       <c r="C38" t="n">
-        <v>98.45</v>
+        <v>23.22</v>
       </c>
       <c r="D38" t="n">
-        <v>12516</v>
+        <v>15084</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>110.22</v>
+        <v>12.61</v>
       </c>
       <c r="B39" t="n">
-        <v>32751</v>
+        <v>28993</v>
       </c>
       <c r="C39" t="n">
-        <v>109.82</v>
+        <v>5.39</v>
       </c>
       <c r="D39" t="n">
-        <v>18758</v>
+        <v>14075</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>92.55</v>
+        <v>12.61</v>
       </c>
       <c r="B40" t="n">
-        <v>27252</v>
+        <v>27497</v>
       </c>
       <c r="C40" t="n">
-        <v>95.14</v>
+        <v>13</v>
       </c>
       <c r="D40" t="n">
-        <v>14568</v>
+        <v>18092</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>91.63</v>
+        <v>13.92</v>
       </c>
       <c r="B41" t="n">
-        <v>23256</v>
+        <v>26917</v>
       </c>
       <c r="C41" t="n">
-        <v>89.45</v>
+        <v>15.07</v>
       </c>
       <c r="D41" t="n">
-        <v>10959</v>
+        <v>25098</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>101.77</v>
+        <v>14.13</v>
       </c>
       <c r="B42" t="n">
-        <v>46479</v>
+        <v>27708</v>
       </c>
       <c r="C42" t="n">
-        <v>103.52</v>
+        <v>17.15</v>
       </c>
       <c r="D42" t="n">
-        <v>16661</v>
+        <v>29807</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110.9</v>
+        <v>14.13</v>
       </c>
       <c r="B43" t="n">
-        <v>29336</v>
+        <v>23410</v>
       </c>
       <c r="C43" t="n">
-        <v>109.5</v>
+        <v>25.77</v>
       </c>
       <c r="D43" t="n">
-        <v>21694</v>
+        <v>11257</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>92.79000000000001</v>
+        <v>14.46</v>
       </c>
       <c r="B44" t="n">
-        <v>28931</v>
+        <v>25661</v>
       </c>
       <c r="C44" t="n">
-        <v>90.95999999999999</v>
+        <v>11.34</v>
       </c>
       <c r="D44" t="n">
-        <v>24358</v>
+        <v>13515</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>116.23</v>
+        <v>15.01</v>
       </c>
       <c r="B45" t="n">
-        <v>25336</v>
+        <v>22801</v>
       </c>
       <c r="C45" t="n">
-        <v>120.68</v>
+        <v>11.01</v>
       </c>
       <c r="D45" t="n">
-        <v>19714</v>
+        <v>26739</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>49.62</v>
+        <v>15.11</v>
       </c>
       <c r="B46" t="n">
-        <v>24141</v>
+        <v>27209</v>
       </c>
       <c r="C46" t="n">
-        <v>52.82</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>23155</v>
+        <v>22531</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104.64</v>
+        <v>15.17</v>
       </c>
       <c r="B47" t="n">
-        <v>48450</v>
+        <v>25179</v>
       </c>
       <c r="C47" t="n">
-        <v>106.9</v>
+        <v>17.48</v>
       </c>
       <c r="D47" t="n">
-        <v>28838</v>
+        <v>28770</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111.71</v>
+        <v>16.04</v>
       </c>
       <c r="B48" t="n">
-        <v>27336</v>
+        <v>25233</v>
       </c>
       <c r="C48" t="n">
-        <v>115.16</v>
+        <v>24.83</v>
       </c>
       <c r="D48" t="n">
-        <v>27567</v>
+        <v>21629</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>101.11</v>
+        <v>16.32</v>
       </c>
       <c r="B49" t="n">
-        <v>43137</v>
+        <v>22381</v>
       </c>
       <c r="C49" t="n">
-        <v>100.68</v>
+        <v>24.13</v>
       </c>
       <c r="D49" t="n">
-        <v>22515</v>
+        <v>11787</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>110.9</v>
+        <v>16.32</v>
       </c>
       <c r="B50" t="n">
-        <v>30500</v>
+        <v>25458</v>
       </c>
       <c r="C50" t="n">
-        <v>108.27</v>
+        <v>21.7</v>
       </c>
       <c r="D50" t="n">
-        <v>11205</v>
+        <v>14480</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>97.31</v>
+        <v>16.75</v>
       </c>
       <c r="B51" t="n">
-        <v>37275</v>
+        <v>22989</v>
       </c>
       <c r="C51" t="n">
-        <v>98.16</v>
+        <v>21.94</v>
       </c>
       <c r="D51" t="n">
-        <v>14202</v>
+        <v>10085</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>109.15</v>
+        <v>17.04</v>
       </c>
       <c r="B52" t="n">
-        <v>34459</v>
+        <v>24266</v>
       </c>
       <c r="C52" t="n">
-        <v>105.98</v>
+        <v>18.28</v>
       </c>
       <c r="D52" t="n">
-        <v>25112</v>
+        <v>28087</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.6</v>
+        <v>17.35</v>
       </c>
       <c r="B53" t="n">
-        <v>25404</v>
+        <v>25231</v>
       </c>
       <c r="C53" t="n">
-        <v>1.58</v>
+        <v>26</v>
       </c>
       <c r="D53" t="n">
-        <v>19040</v>
+        <v>24978</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>114.69</v>
+        <v>17.4</v>
       </c>
       <c r="B54" t="n">
-        <v>23386</v>
+        <v>24559</v>
       </c>
       <c r="C54" t="n">
-        <v>119.03</v>
+        <v>18.13</v>
       </c>
       <c r="D54" t="n">
-        <v>22566</v>
+        <v>26825</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>139.27</v>
+        <v>17.43</v>
       </c>
       <c r="B55" t="n">
-        <v>25587</v>
+        <v>24052</v>
       </c>
       <c r="C55" t="n">
-        <v>142.41</v>
+        <v>13.17</v>
       </c>
       <c r="D55" t="n">
-        <v>14478</v>
+        <v>21849</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>109.57</v>
+        <v>18.06</v>
       </c>
       <c r="B56" t="n">
-        <v>34200</v>
+        <v>26665</v>
       </c>
       <c r="C56" t="n">
-        <v>111.62</v>
+        <v>20.19</v>
       </c>
       <c r="D56" t="n">
-        <v>24733</v>
+        <v>29634</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>11.36</v>
+        <v>18.35</v>
       </c>
       <c r="B57" t="n">
-        <v>23883</v>
+        <v>25091</v>
       </c>
       <c r="C57" t="n">
-        <v>11.54</v>
+        <v>20.94</v>
       </c>
       <c r="D57" t="n">
-        <v>29061</v>
+        <v>17495</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>50.4</v>
+        <v>18.66</v>
       </c>
       <c r="B58" t="n">
-        <v>21951</v>
+        <v>22583</v>
       </c>
       <c r="C58" t="n">
-        <v>51.06</v>
+        <v>10.7</v>
       </c>
       <c r="D58" t="n">
-        <v>20102</v>
+        <v>13446</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>94.26000000000001</v>
+        <v>19.53</v>
       </c>
       <c r="B59" t="n">
-        <v>32612</v>
+        <v>26117</v>
       </c>
       <c r="C59" t="n">
-        <v>92.43000000000001</v>
+        <v>12.38</v>
       </c>
       <c r="D59" t="n">
-        <v>16182</v>
+        <v>18571</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>95.09999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="B60" t="n">
-        <v>34978</v>
+        <v>22043</v>
       </c>
       <c r="C60" t="n">
-        <v>91.98999999999999</v>
+        <v>21.45</v>
       </c>
       <c r="D60" t="n">
-        <v>17510</v>
+        <v>17768</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>111.42</v>
+        <v>20.01</v>
       </c>
       <c r="B61" t="n">
-        <v>28653</v>
+        <v>24804</v>
       </c>
       <c r="C61" t="n">
-        <v>109.83</v>
+        <v>28.07</v>
       </c>
       <c r="D61" t="n">
-        <v>20074</v>
+        <v>12810</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>110.7</v>
+        <v>21.28</v>
       </c>
       <c r="B62" t="n">
-        <v>29648</v>
+        <v>20633</v>
       </c>
       <c r="C62" t="n">
-        <v>113.46</v>
+        <v>15.32</v>
       </c>
       <c r="D62" t="n">
-        <v>14745</v>
+        <v>17677</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>108.24</v>
+        <v>21.68</v>
       </c>
       <c r="B63" t="n">
-        <v>40285</v>
+        <v>23288</v>
       </c>
       <c r="C63" t="n">
-        <v>110.51</v>
+        <v>15.96</v>
       </c>
       <c r="D63" t="n">
-        <v>26347</v>
+        <v>27820</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>28.14</v>
+        <v>22.12</v>
       </c>
       <c r="B64" t="n">
-        <v>24417</v>
+        <v>20988</v>
       </c>
       <c r="C64" t="n">
-        <v>28.29</v>
+        <v>24.65</v>
       </c>
       <c r="D64" t="n">
-        <v>15143</v>
+        <v>23044</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>98.94</v>
+        <v>22.67</v>
       </c>
       <c r="B65" t="n">
-        <v>41705</v>
+        <v>24065</v>
       </c>
       <c r="C65" t="n">
-        <v>96.33</v>
+        <v>19.81</v>
       </c>
       <c r="D65" t="n">
-        <v>25785</v>
+        <v>14801</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>110.6</v>
+        <v>23.07</v>
       </c>
       <c r="B66" t="n">
-        <v>30132</v>
+        <v>21710</v>
       </c>
       <c r="C66" t="n">
-        <v>109.96</v>
+        <v>20.15</v>
       </c>
       <c r="D66" t="n">
-        <v>27881</v>
+        <v>16905</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>57.99</v>
+        <v>23.6</v>
       </c>
       <c r="B67" t="n">
-        <v>21204</v>
+        <v>21335</v>
       </c>
       <c r="C67" t="n">
-        <v>60.43</v>
+        <v>12.95</v>
       </c>
       <c r="D67" t="n">
-        <v>18175</v>
+        <v>14859</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>93.95999999999999</v>
+        <v>24.09</v>
       </c>
       <c r="B68" t="n">
-        <v>28526</v>
+        <v>22530</v>
       </c>
       <c r="C68" t="n">
-        <v>94.33</v>
+        <v>15.49</v>
       </c>
       <c r="D68" t="n">
-        <v>18160</v>
+        <v>25697</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>98.64</v>
+        <v>24.51</v>
       </c>
       <c r="B69" t="n">
-        <v>45700</v>
+        <v>23838</v>
       </c>
       <c r="C69" t="n">
-        <v>98.09</v>
+        <v>17.14</v>
       </c>
       <c r="D69" t="n">
-        <v>18208</v>
+        <v>29642</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>100.22</v>
+        <v>24.56</v>
       </c>
       <c r="B70" t="n">
-        <v>48308</v>
+        <v>19524</v>
       </c>
       <c r="C70" t="n">
-        <v>97.95</v>
+        <v>27.6</v>
       </c>
       <c r="D70" t="n">
-        <v>19623</v>
+        <v>25078</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>105.79</v>
+        <v>24.97</v>
       </c>
       <c r="B71" t="n">
-        <v>45491</v>
+        <v>23402</v>
       </c>
       <c r="C71" t="n">
-        <v>105.58</v>
+        <v>32.73</v>
       </c>
       <c r="D71" t="n">
-        <v>19934</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>138.72</v>
+        <v>25.18</v>
       </c>
       <c r="B72" t="n">
-        <v>25170</v>
+        <v>21462</v>
       </c>
       <c r="C72" t="n">
-        <v>142.86</v>
+        <v>24.26</v>
       </c>
       <c r="D72" t="n">
-        <v>12828</v>
+        <v>21024</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>107.52</v>
+        <v>25.56</v>
       </c>
       <c r="B73" t="n">
-        <v>43519</v>
+        <v>20303</v>
       </c>
       <c r="C73" t="n">
-        <v>106.74</v>
+        <v>25.72</v>
       </c>
       <c r="D73" t="n">
-        <v>12028</v>
+        <v>23502</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>114.77</v>
+        <v>26.6</v>
       </c>
       <c r="B74" t="n">
-        <v>20095</v>
+        <v>19472</v>
       </c>
       <c r="C74" t="n">
-        <v>118.65</v>
+        <v>15.13</v>
       </c>
       <c r="D74" t="n">
-        <v>28962</v>
+        <v>25925</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112.04</v>
+        <v>26.9</v>
       </c>
       <c r="B75" t="n">
-        <v>28387</v>
+        <v>20656</v>
       </c>
       <c r="C75" t="n">
-        <v>111.97</v>
+        <v>23.55</v>
       </c>
       <c r="D75" t="n">
-        <v>25258</v>
+        <v>14964</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>159.05</v>
+        <v>27.15</v>
       </c>
       <c r="B76" t="n">
-        <v>24614</v>
+        <v>21833</v>
       </c>
       <c r="C76" t="n">
-        <v>159.63</v>
+        <v>38.87</v>
       </c>
       <c r="D76" t="n">
-        <v>16635</v>
+        <v>27522</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>103.65</v>
+        <v>27.25</v>
       </c>
       <c r="B77" t="n">
-        <v>43707</v>
+        <v>19798</v>
       </c>
       <c r="C77" t="n">
-        <v>106.9</v>
+        <v>27.31</v>
       </c>
       <c r="D77" t="n">
-        <v>27171</v>
+        <v>19936</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113.24</v>
+        <v>27.42</v>
       </c>
       <c r="B78" t="n">
-        <v>25644</v>
+        <v>22139</v>
       </c>
       <c r="C78" t="n">
-        <v>115.5</v>
+        <v>33.12</v>
       </c>
       <c r="D78" t="n">
-        <v>16549</v>
+        <v>14534</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>105.22</v>
+        <v>27.61</v>
       </c>
       <c r="B79" t="n">
-        <v>46456</v>
+        <v>24915</v>
       </c>
       <c r="C79" t="n">
-        <v>104.13</v>
+        <v>27.34</v>
       </c>
       <c r="D79" t="n">
-        <v>25006</v>
+        <v>15223</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112.75</v>
+        <v>27.81</v>
       </c>
       <c r="B80" t="n">
-        <v>25054</v>
+        <v>21475</v>
       </c>
       <c r="C80" t="n">
-        <v>114.71</v>
+        <v>24.73</v>
       </c>
       <c r="D80" t="n">
-        <v>26780</v>
+        <v>21152</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>104.08</v>
+        <v>28.18</v>
       </c>
       <c r="B81" t="n">
-        <v>46044</v>
+        <v>21052</v>
       </c>
       <c r="C81" t="n">
-        <v>107.34</v>
+        <v>15.71</v>
       </c>
       <c r="D81" t="n">
-        <v>17462</v>
+        <v>23433</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>94.79000000000001</v>
+        <v>28.28</v>
       </c>
       <c r="B82" t="n">
-        <v>33086</v>
+        <v>21921</v>
       </c>
       <c r="C82" t="n">
-        <v>94.25</v>
+        <v>24.95</v>
       </c>
       <c r="D82" t="n">
-        <v>15260</v>
+        <v>21563</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>111.56</v>
+        <v>29.56</v>
       </c>
       <c r="B83" t="n">
-        <v>28100</v>
+        <v>21959</v>
       </c>
       <c r="C83" t="n">
-        <v>116.03</v>
+        <v>33.9</v>
       </c>
       <c r="D83" t="n">
-        <v>21197</v>
+        <v>26946</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>109.56</v>
+        <v>29.72</v>
       </c>
       <c r="B84" t="n">
-        <v>33932</v>
+        <v>18903</v>
       </c>
       <c r="C84" t="n">
-        <v>108.63</v>
+        <v>34.6</v>
       </c>
       <c r="D84" t="n">
-        <v>18345</v>
+        <v>28693</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>104.12</v>
+        <v>29.72</v>
       </c>
       <c r="B85" t="n">
-        <v>47543</v>
+        <v>22084</v>
       </c>
       <c r="C85" t="n">
-        <v>99.26000000000001</v>
+        <v>23.14</v>
       </c>
       <c r="D85" t="n">
-        <v>26147</v>
+        <v>26307</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>94.68000000000001</v>
+        <v>29.73</v>
       </c>
       <c r="B86" t="n">
-        <v>32753</v>
+        <v>23410</v>
       </c>
       <c r="C86" t="n">
-        <v>97.44</v>
+        <v>28.74</v>
       </c>
       <c r="D86" t="n">
-        <v>13044</v>
+        <v>28504</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>97.84</v>
+        <v>30.6</v>
       </c>
       <c r="B87" t="n">
-        <v>40767</v>
+        <v>19564</v>
       </c>
       <c r="C87" t="n">
-        <v>100.93</v>
+        <v>31.3</v>
       </c>
       <c r="D87" t="n">
-        <v>25382</v>
+        <v>14676</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>98.27</v>
+        <v>30.98</v>
       </c>
       <c r="B88" t="n">
-        <v>39420</v>
+        <v>23405</v>
       </c>
       <c r="C88" t="n">
-        <v>98.64</v>
+        <v>32.59</v>
       </c>
       <c r="D88" t="n">
-        <v>17643</v>
+        <v>14032</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>97.90000000000001</v>
+        <v>31.16</v>
       </c>
       <c r="B89" t="n">
-        <v>39828</v>
+        <v>22035</v>
       </c>
       <c r="C89" t="n">
-        <v>97.19</v>
+        <v>28.05</v>
       </c>
       <c r="D89" t="n">
-        <v>11407</v>
+        <v>14732</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>108.8</v>
+        <v>31.38</v>
       </c>
       <c r="B90" t="n">
-        <v>36246</v>
+        <v>21108</v>
       </c>
       <c r="C90" t="n">
-        <v>110.61</v>
+        <v>32.92</v>
       </c>
       <c r="D90" t="n">
-        <v>17867</v>
+        <v>23546</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>95.45999999999999</v>
+        <v>31.43</v>
       </c>
       <c r="B91" t="n">
-        <v>34562</v>
+        <v>20902</v>
       </c>
       <c r="C91" t="n">
-        <v>95.67</v>
+        <v>36.8</v>
       </c>
       <c r="D91" t="n">
-        <v>29894</v>
+        <v>20973</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>113.63</v>
+        <v>31.67</v>
       </c>
       <c r="B92" t="n">
-        <v>22698</v>
+        <v>18429</v>
       </c>
       <c r="C92" t="n">
-        <v>116.6</v>
+        <v>40.6</v>
       </c>
       <c r="D92" t="n">
-        <v>12615</v>
+        <v>17965</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>91.02</v>
+        <v>31.79</v>
       </c>
       <c r="B93" t="n">
-        <v>23929</v>
+        <v>20725</v>
       </c>
       <c r="C93" t="n">
-        <v>94.91</v>
+        <v>39.46</v>
       </c>
       <c r="D93" t="n">
-        <v>13538</v>
+        <v>24726</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>103.72</v>
+        <v>32.07</v>
       </c>
       <c r="B94" t="n">
-        <v>46328</v>
+        <v>22814</v>
       </c>
       <c r="C94" t="n">
-        <v>103.79</v>
+        <v>28.88</v>
       </c>
       <c r="D94" t="n">
-        <v>13203</v>
+        <v>21334</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>90.72</v>
+        <v>32.22</v>
       </c>
       <c r="B95" t="n">
-        <v>23378</v>
+        <v>20602</v>
       </c>
       <c r="C95" t="n">
-        <v>89.15000000000001</v>
+        <v>26.61</v>
       </c>
       <c r="D95" t="n">
-        <v>28071</v>
+        <v>16661</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>101.79</v>
+        <v>32.52</v>
       </c>
       <c r="B96" t="n">
-        <v>48724</v>
+        <v>19607</v>
       </c>
       <c r="C96" t="n">
-        <v>96.91</v>
+        <v>31.79</v>
       </c>
       <c r="D96" t="n">
-        <v>24283</v>
+        <v>18274</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>51.2</v>
+        <v>33.39</v>
       </c>
       <c r="B97" t="n">
-        <v>25234</v>
+        <v>24422</v>
       </c>
       <c r="C97" t="n">
-        <v>52.61</v>
+        <v>32.97</v>
       </c>
       <c r="D97" t="n">
-        <v>20433</v>
+        <v>19909</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>96.48999999999999</v>
+        <v>33.76</v>
       </c>
       <c r="B98" t="n">
-        <v>37718</v>
+        <v>22285</v>
       </c>
       <c r="C98" t="n">
-        <v>94.18000000000001</v>
+        <v>29.97</v>
       </c>
       <c r="D98" t="n">
-        <v>10994</v>
+        <v>29530</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>95.42</v>
+        <v>36.29</v>
       </c>
       <c r="B99" t="n">
-        <v>32282</v>
+        <v>19674</v>
       </c>
       <c r="C99" t="n">
-        <v>98.56</v>
+        <v>26.2</v>
       </c>
       <c r="D99" t="n">
-        <v>11267</v>
+        <v>18906</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>56.57</v>
+        <v>36.64</v>
       </c>
       <c r="B100" t="n">
-        <v>25256</v>
+        <v>20861</v>
       </c>
       <c r="C100" t="n">
-        <v>58.35</v>
+        <v>34.19</v>
       </c>
       <c r="D100" t="n">
-        <v>11130</v>
+        <v>23763</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>98.91</v>
+        <v>38.02</v>
       </c>
       <c r="B101" t="n">
-        <v>39960</v>
+        <v>20107</v>
       </c>
       <c r="C101" t="n">
-        <v>99.8</v>
+        <v>46</v>
       </c>
       <c r="D101" t="n">
-        <v>12232</v>
+        <v>29814</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>114.91</v>
+        <v>38.15</v>
       </c>
       <c r="B102" t="n">
-        <v>26131</v>
+        <v>20207</v>
       </c>
       <c r="C102" t="n">
-        <v>117.97</v>
+        <v>39.09</v>
       </c>
       <c r="D102" t="n">
-        <v>16201</v>
+        <v>14563</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>95.73999999999999</v>
+        <v>38.33</v>
       </c>
       <c r="B103" t="n">
-        <v>35397</v>
+        <v>21957</v>
       </c>
       <c r="C103" t="n">
-        <v>97.53</v>
+        <v>51.18</v>
       </c>
       <c r="D103" t="n">
-        <v>16072</v>
+        <v>15299</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>107.73</v>
+        <v>38.39</v>
       </c>
       <c r="B104" t="n">
-        <v>39258</v>
+        <v>21804</v>
       </c>
       <c r="C104" t="n">
-        <v>103.16</v>
+        <v>27.1</v>
       </c>
       <c r="D104" t="n">
-        <v>12637</v>
+        <v>28896</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>53.31</v>
+        <v>39.53</v>
       </c>
       <c r="B105" t="n">
-        <v>23512</v>
+        <v>24431</v>
       </c>
       <c r="C105" t="n">
-        <v>53.11</v>
+        <v>37.22</v>
       </c>
       <c r="D105" t="n">
-        <v>21758</v>
+        <v>22026</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>109.19</v>
+        <v>39.79</v>
       </c>
       <c r="B106" t="n">
-        <v>32865</v>
+        <v>21758</v>
       </c>
       <c r="C106" t="n">
-        <v>107.73</v>
+        <v>38.05</v>
       </c>
       <c r="D106" t="n">
-        <v>27068</v>
+        <v>26093</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>108.8</v>
+        <v>39.91</v>
       </c>
       <c r="B107" t="n">
-        <v>34849</v>
+        <v>21098</v>
       </c>
       <c r="C107" t="n">
-        <v>107.01</v>
+        <v>38.66</v>
       </c>
       <c r="D107" t="n">
-        <v>17328</v>
+        <v>21239</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>90.01000000000001</v>
+        <v>40.08</v>
       </c>
       <c r="B108" t="n">
-        <v>23122</v>
+        <v>19048</v>
       </c>
       <c r="C108" t="n">
-        <v>93.08</v>
+        <v>23.29</v>
       </c>
       <c r="D108" t="n">
-        <v>22907</v>
+        <v>10411</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>94.94</v>
+        <v>40.15</v>
       </c>
       <c r="B109" t="n">
-        <v>32174</v>
+        <v>23906</v>
       </c>
       <c r="C109" t="n">
-        <v>95.89</v>
+        <v>35.59</v>
       </c>
       <c r="D109" t="n">
-        <v>16176</v>
+        <v>29287</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>109.23</v>
+        <v>40.15</v>
       </c>
       <c r="B110" t="n">
-        <v>34931</v>
+        <v>22292</v>
       </c>
       <c r="C110" t="n">
-        <v>105.79</v>
+        <v>41.68</v>
       </c>
       <c r="D110" t="n">
-        <v>22161</v>
+        <v>17088</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>110.65</v>
+        <v>40.32</v>
       </c>
       <c r="B111" t="n">
-        <v>29813</v>
+        <v>21585</v>
       </c>
       <c r="C111" t="n">
-        <v>111.92</v>
+        <v>38.49</v>
       </c>
       <c r="D111" t="n">
-        <v>14726</v>
+        <v>17723</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>111.42</v>
+        <v>40.7</v>
       </c>
       <c r="B112" t="n">
-        <v>27590</v>
+        <v>22064</v>
       </c>
       <c r="C112" t="n">
-        <v>116.2</v>
+        <v>32.41</v>
       </c>
       <c r="D112" t="n">
-        <v>18075</v>
+        <v>10250</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>23.25</v>
+        <v>40.92</v>
       </c>
       <c r="B113" t="n">
-        <v>22009</v>
+        <v>23333</v>
       </c>
       <c r="C113" t="n">
-        <v>22.95</v>
+        <v>20.17</v>
       </c>
       <c r="D113" t="n">
-        <v>13099</v>
+        <v>27986</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>97.26000000000001</v>
+        <v>42.04</v>
       </c>
       <c r="B114" t="n">
-        <v>39099</v>
+        <v>19852</v>
       </c>
       <c r="C114" t="n">
-        <v>100.81</v>
+        <v>39.13</v>
       </c>
       <c r="D114" t="n">
-        <v>25394</v>
+        <v>13165</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>107.42</v>
+        <v>43</v>
       </c>
       <c r="B115" t="n">
-        <v>42113</v>
+        <v>19490</v>
       </c>
       <c r="C115" t="n">
-        <v>107.79</v>
+        <v>46.27</v>
       </c>
       <c r="D115" t="n">
-        <v>16325</v>
+        <v>14685</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>99.8</v>
+        <v>43.44</v>
       </c>
       <c r="B116" t="n">
-        <v>45802</v>
+        <v>20438</v>
       </c>
       <c r="C116" t="n">
-        <v>97.19</v>
+        <v>49.1</v>
       </c>
       <c r="D116" t="n">
-        <v>27889</v>
+        <v>16664</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>93.81999999999999</v>
+        <v>43.57</v>
       </c>
       <c r="B117" t="n">
-        <v>29851</v>
+        <v>21778</v>
       </c>
       <c r="C117" t="n">
-        <v>90.59999999999999</v>
+        <v>38.3</v>
       </c>
       <c r="D117" t="n">
-        <v>26173</v>
+        <v>17101</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>109.47</v>
+        <v>44.21</v>
       </c>
       <c r="B118" t="n">
-        <v>31908</v>
+        <v>22603</v>
       </c>
       <c r="C118" t="n">
-        <v>106.21</v>
+        <v>36.09</v>
       </c>
       <c r="D118" t="n">
-        <v>26989</v>
+        <v>20179</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>97.51000000000001</v>
+        <v>44.35</v>
       </c>
       <c r="B119" t="n">
-        <v>39222</v>
+        <v>23088</v>
       </c>
       <c r="C119" t="n">
-        <v>97.08</v>
+        <v>50.47</v>
       </c>
       <c r="D119" t="n">
-        <v>12787</v>
+        <v>13467</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>105.91</v>
+        <v>44.62</v>
       </c>
       <c r="B120" t="n">
-        <v>42780</v>
+        <v>22130</v>
       </c>
       <c r="C120" t="n">
-        <v>109.52</v>
+        <v>46.87</v>
       </c>
       <c r="D120" t="n">
-        <v>18282</v>
+        <v>19647</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>94.8</v>
+        <v>44.92</v>
       </c>
       <c r="B121" t="n">
-        <v>34650</v>
+        <v>20550</v>
       </c>
       <c r="C121" t="n">
-        <v>96.97</v>
+        <v>44.94</v>
       </c>
       <c r="D121" t="n">
-        <v>25941</v>
+        <v>11749</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>94.8</v>
+        <v>45.09</v>
       </c>
       <c r="B122" t="n">
-        <v>30018</v>
+        <v>22530</v>
       </c>
       <c r="C122" t="n">
-        <v>91.86</v>
+        <v>53.67</v>
       </c>
       <c r="D122" t="n">
-        <v>23711</v>
+        <v>15843</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>104.6</v>
+        <v>45.09</v>
       </c>
       <c r="B123" t="n">
-        <v>46433</v>
+        <v>21781</v>
       </c>
       <c r="C123" t="n">
-        <v>101.84</v>
+        <v>53.4</v>
       </c>
       <c r="D123" t="n">
-        <v>16125</v>
+        <v>14505</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>90.48</v>
+        <v>45.43</v>
       </c>
       <c r="B124" t="n">
-        <v>21961</v>
+        <v>20810</v>
       </c>
       <c r="C124" t="n">
-        <v>91.19</v>
+        <v>52.47</v>
       </c>
       <c r="D124" t="n">
-        <v>29213</v>
+        <v>21230</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>109.51</v>
+        <v>45.59</v>
       </c>
       <c r="B125" t="n">
-        <v>34206</v>
+        <v>20905</v>
       </c>
       <c r="C125" t="n">
-        <v>107.18</v>
+        <v>40.9</v>
       </c>
       <c r="D125" t="n">
-        <v>17111</v>
+        <v>25255</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>111.31</v>
+        <v>46.1</v>
       </c>
       <c r="B126" t="n">
-        <v>28380</v>
+        <v>22871</v>
       </c>
       <c r="C126" t="n">
-        <v>111.02</v>
+        <v>51.96</v>
       </c>
       <c r="D126" t="n">
-        <v>10594</v>
+        <v>13234</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>101.66</v>
+        <v>46.32</v>
       </c>
       <c r="B127" t="n">
-        <v>45604</v>
+        <v>20752</v>
       </c>
       <c r="C127" t="n">
-        <v>97.55</v>
+        <v>35.46</v>
       </c>
       <c r="D127" t="n">
-        <v>12360</v>
+        <v>17291</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>94.84999999999999</v>
+        <v>46.41</v>
       </c>
       <c r="B128" t="n">
-        <v>33424</v>
+        <v>21893</v>
       </c>
       <c r="C128" t="n">
-        <v>95.17</v>
+        <v>45.34</v>
       </c>
       <c r="D128" t="n">
-        <v>16495</v>
+        <v>17180</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>101.4</v>
+        <v>46.47</v>
       </c>
       <c r="B129" t="n">
-        <v>44801</v>
+        <v>19338</v>
       </c>
       <c r="C129" t="n">
-        <v>104.8</v>
+        <v>36.2</v>
       </c>
       <c r="D129" t="n">
-        <v>12931</v>
+        <v>17356</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>110.82</v>
+        <v>46.76</v>
       </c>
       <c r="B130" t="n">
-        <v>28490</v>
+        <v>20601</v>
       </c>
       <c r="C130" t="n">
-        <v>106.93</v>
+        <v>33.63</v>
       </c>
       <c r="D130" t="n">
-        <v>28411</v>
+        <v>18099</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>110.58</v>
+        <v>47.1</v>
       </c>
       <c r="B131" t="n">
-        <v>30228</v>
+        <v>21412</v>
       </c>
       <c r="C131" t="n">
-        <v>107.52</v>
+        <v>36.13</v>
       </c>
       <c r="D131" t="n">
-        <v>19371</v>
+        <v>14228</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>114.74</v>
+        <v>47.54</v>
       </c>
       <c r="B132" t="n">
-        <v>23967</v>
+        <v>19157</v>
       </c>
       <c r="C132" t="n">
-        <v>112.34</v>
+        <v>40.58</v>
       </c>
       <c r="D132" t="n">
-        <v>24723</v>
+        <v>11663</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>113.73</v>
+        <v>47.86</v>
       </c>
       <c r="B133" t="n">
-        <v>26090</v>
+        <v>23857</v>
       </c>
       <c r="C133" t="n">
-        <v>116.6</v>
+        <v>49.63</v>
       </c>
       <c r="D133" t="n">
-        <v>25098</v>
+        <v>10238</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>112.67</v>
+        <v>48.01</v>
       </c>
       <c r="B134" t="n">
-        <v>28031</v>
+        <v>22762</v>
       </c>
       <c r="C134" t="n">
-        <v>117.12</v>
+        <v>38.01</v>
       </c>
       <c r="D134" t="n">
-        <v>20854</v>
+        <v>22169</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>98.34999999999999</v>
+        <v>48.62</v>
       </c>
       <c r="B135" t="n">
-        <v>42322</v>
+        <v>22874</v>
       </c>
       <c r="C135" t="n">
-        <v>96.79000000000001</v>
+        <v>55.03</v>
       </c>
       <c r="D135" t="n">
-        <v>15485</v>
+        <v>19637</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>139.87</v>
+        <v>48.63</v>
       </c>
       <c r="B136" t="n">
-        <v>24204</v>
+        <v>23064</v>
       </c>
       <c r="C136" t="n">
-        <v>143.61</v>
+        <v>52.79</v>
       </c>
       <c r="D136" t="n">
-        <v>26692</v>
+        <v>25670</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>101.74</v>
+        <v>49.22</v>
       </c>
       <c r="B137" t="n">
-        <v>45094</v>
+        <v>19815</v>
       </c>
       <c r="C137" t="n">
-        <v>105.33</v>
+        <v>44.08</v>
       </c>
       <c r="D137" t="n">
-        <v>17289</v>
+        <v>25156</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>91.23999999999999</v>
+        <v>49.34</v>
       </c>
       <c r="B138" t="n">
-        <v>26263</v>
+        <v>20837</v>
       </c>
       <c r="C138" t="n">
-        <v>93.79000000000001</v>
+        <v>47.25</v>
       </c>
       <c r="D138" t="n">
-        <v>10468</v>
+        <v>11909</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>90.23</v>
+        <v>49.52</v>
       </c>
       <c r="B139" t="n">
-        <v>22110</v>
+        <v>21825</v>
       </c>
       <c r="C139" t="n">
-        <v>92.13</v>
+        <v>48.48</v>
       </c>
       <c r="D139" t="n">
-        <v>25928</v>
+        <v>27148</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>90.98</v>
+        <v>49.6</v>
       </c>
       <c r="B140" t="n">
-        <v>24256</v>
+        <v>20808</v>
       </c>
       <c r="C140" t="n">
-        <v>88.90000000000001</v>
+        <v>55.95</v>
       </c>
       <c r="D140" t="n">
-        <v>24772</v>
+        <v>13137</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>95.51000000000001</v>
+        <v>49.66</v>
       </c>
       <c r="B141" t="n">
-        <v>35527</v>
+        <v>18438</v>
       </c>
       <c r="C141" t="n">
-        <v>95.51000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="D141" t="n">
-        <v>12529</v>
+        <v>13624</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>105.41</v>
+        <v>50.32</v>
       </c>
       <c r="B142" t="n">
-        <v>45442</v>
+        <v>20288</v>
       </c>
       <c r="C142" t="n">
-        <v>102.24</v>
+        <v>63.89</v>
       </c>
       <c r="D142" t="n">
-        <v>27453</v>
+        <v>23341</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>106.54</v>
+        <v>50.81</v>
       </c>
       <c r="B143" t="n">
-        <v>41780</v>
+        <v>20716</v>
       </c>
       <c r="C143" t="n">
-        <v>103.55</v>
+        <v>51.42</v>
       </c>
       <c r="D143" t="n">
-        <v>17784</v>
+        <v>10551</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>103.01</v>
+        <v>51.04</v>
       </c>
       <c r="B144" t="n">
-        <v>48674</v>
+        <v>18451</v>
       </c>
       <c r="C144" t="n">
-        <v>102.06</v>
+        <v>51.59</v>
       </c>
       <c r="D144" t="n">
-        <v>15021</v>
+        <v>27966</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>92.06</v>
+        <v>51.42</v>
       </c>
       <c r="B145" t="n">
-        <v>27640</v>
+        <v>22410</v>
       </c>
       <c r="C145" t="n">
-        <v>91.23</v>
+        <v>48.93</v>
       </c>
       <c r="D145" t="n">
-        <v>16594</v>
+        <v>28840</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>96.41</v>
+        <v>51.67</v>
       </c>
       <c r="B146" t="n">
-        <v>38851</v>
+        <v>20953</v>
       </c>
       <c r="C146" t="n">
-        <v>95.38</v>
+        <v>39.66</v>
       </c>
       <c r="D146" t="n">
-        <v>22724</v>
+        <v>25004</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>150.11</v>
+        <v>51.91</v>
       </c>
       <c r="B147" t="n">
-        <v>24369</v>
+        <v>22176</v>
       </c>
       <c r="C147" t="n">
-        <v>146.4</v>
+        <v>35.05</v>
       </c>
       <c r="D147" t="n">
-        <v>21946</v>
+        <v>14221</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>93.26000000000001</v>
+        <v>52.06</v>
       </c>
       <c r="B148" t="n">
-        <v>28317</v>
+        <v>19960</v>
       </c>
       <c r="C148" t="n">
-        <v>96</v>
+        <v>32.38</v>
       </c>
       <c r="D148" t="n">
-        <v>20285</v>
+        <v>17477</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>112.62</v>
+        <v>54.35</v>
       </c>
       <c r="B149" t="n">
-        <v>25381</v>
+        <v>22173</v>
       </c>
       <c r="C149" t="n">
-        <v>109.23</v>
+        <v>62.77</v>
       </c>
       <c r="D149" t="n">
-        <v>14009</v>
+        <v>19439</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>111.74</v>
+        <v>54.46</v>
       </c>
       <c r="B150" t="n">
-        <v>25125</v>
+        <v>22151</v>
       </c>
       <c r="C150" t="n">
-        <v>115.29</v>
+        <v>52.04</v>
       </c>
       <c r="D150" t="n">
-        <v>26302</v>
+        <v>27485</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>108.02</v>
+        <v>54.61</v>
       </c>
       <c r="B151" t="n">
-        <v>35999</v>
+        <v>22887</v>
       </c>
       <c r="C151" t="n">
-        <v>108.32</v>
+        <v>57.11</v>
       </c>
       <c r="D151" t="n">
-        <v>11615</v>
+        <v>11279</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>113.39</v>
+        <v>54.92</v>
       </c>
       <c r="B152" t="n">
-        <v>25737</v>
+        <v>18229</v>
       </c>
       <c r="C152" t="n">
-        <v>111.03</v>
+        <v>59.78</v>
       </c>
       <c r="D152" t="n">
-        <v>11655</v>
+        <v>10354</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>91.89</v>
+        <v>55.86</v>
       </c>
       <c r="B153" t="n">
-        <v>28207</v>
+        <v>22291</v>
       </c>
       <c r="C153" t="n">
-        <v>94.43000000000001</v>
+        <v>44.03</v>
       </c>
       <c r="D153" t="n">
-        <v>25135</v>
+        <v>28483</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>103.11</v>
+        <v>56.02</v>
       </c>
       <c r="B154" t="n">
-        <v>47853</v>
+        <v>22038</v>
       </c>
       <c r="C154" t="n">
-        <v>106.26</v>
+        <v>58.25</v>
       </c>
       <c r="D154" t="n">
-        <v>26467</v>
+        <v>13207</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>98.90000000000001</v>
+        <v>56.06</v>
       </c>
       <c r="B155" t="n">
-        <v>45032</v>
+        <v>19514</v>
       </c>
       <c r="C155" t="n">
-        <v>103.09</v>
+        <v>44.78</v>
       </c>
       <c r="D155" t="n">
-        <v>20515</v>
+        <v>23523</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>96.04000000000001</v>
+        <v>56.22</v>
       </c>
       <c r="B156" t="n">
-        <v>36770</v>
+        <v>22155</v>
       </c>
       <c r="C156" t="n">
-        <v>93.73</v>
+        <v>42.12</v>
       </c>
       <c r="D156" t="n">
-        <v>12472</v>
+        <v>29103</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>93.5</v>
+        <v>56.25</v>
       </c>
       <c r="B157" t="n">
-        <v>26748</v>
+        <v>21881</v>
       </c>
       <c r="C157" t="n">
-        <v>97.94</v>
+        <v>53.59</v>
       </c>
       <c r="D157" t="n">
-        <v>23233</v>
+        <v>26614</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>107.52</v>
+        <v>56.81</v>
       </c>
       <c r="B158" t="n">
-        <v>37609</v>
+        <v>20860</v>
       </c>
       <c r="C158" t="n">
-        <v>104.23</v>
+        <v>62.37</v>
       </c>
       <c r="D158" t="n">
-        <v>11681</v>
+        <v>19644</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>104.05</v>
+        <v>57.21</v>
       </c>
       <c r="B159" t="n">
-        <v>47808</v>
+        <v>22461</v>
       </c>
       <c r="C159" t="n">
-        <v>103.82</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D159" t="n">
-        <v>13253</v>
+        <v>13671</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>90.64</v>
+        <v>57.76</v>
       </c>
       <c r="B160" t="n">
-        <v>26599</v>
+        <v>19754</v>
       </c>
       <c r="C160" t="n">
-        <v>93.94</v>
+        <v>48.47</v>
       </c>
       <c r="D160" t="n">
-        <v>19462</v>
+        <v>17932</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>99.34999999999999</v>
+        <v>57.84</v>
       </c>
       <c r="B161" t="n">
-        <v>43290</v>
+        <v>20910</v>
       </c>
       <c r="C161" t="n">
-        <v>98.83</v>
+        <v>62.49</v>
       </c>
       <c r="D161" t="n">
-        <v>13655</v>
+        <v>13127</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>112.63</v>
+        <v>58.25</v>
       </c>
       <c r="B162" t="n">
-        <v>27756</v>
+        <v>21093</v>
       </c>
       <c r="C162" t="n">
-        <v>114.36</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="D162" t="n">
-        <v>13551</v>
+        <v>16156</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>19.68</v>
+        <v>58.39</v>
       </c>
       <c r="B163" t="n">
-        <v>22321</v>
+        <v>21099</v>
       </c>
       <c r="C163" t="n">
-        <v>19.24</v>
+        <v>53.11</v>
       </c>
       <c r="D163" t="n">
-        <v>13676</v>
+        <v>13148</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>104.02</v>
+        <v>58.79</v>
       </c>
       <c r="B164" t="n">
-        <v>46265</v>
+        <v>21320</v>
       </c>
       <c r="C164" t="n">
-        <v>104.89</v>
+        <v>52.28</v>
       </c>
       <c r="D164" t="n">
-        <v>14775</v>
+        <v>27025</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>93.75</v>
+        <v>58.9</v>
       </c>
       <c r="B165" t="n">
-        <v>29598</v>
+        <v>21013</v>
       </c>
       <c r="C165" t="n">
-        <v>96.22</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="D165" t="n">
-        <v>13855</v>
+        <v>24912</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>100.78</v>
+        <v>59.12</v>
       </c>
       <c r="B166" t="n">
-        <v>45498</v>
+        <v>22426</v>
       </c>
       <c r="C166" t="n">
-        <v>104.82</v>
+        <v>51.15</v>
       </c>
       <c r="D166" t="n">
-        <v>14712</v>
+        <v>12623</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>11.1</v>
+        <v>60.44</v>
       </c>
       <c r="B167" t="n">
-        <v>21614</v>
+        <v>22171</v>
       </c>
       <c r="C167" t="n">
-        <v>10.56</v>
+        <v>44.24</v>
       </c>
       <c r="D167" t="n">
-        <v>29606</v>
+        <v>12958</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>113</v>
+        <v>61.04</v>
       </c>
       <c r="B168" t="n">
-        <v>25748</v>
+        <v>22163</v>
       </c>
       <c r="C168" t="n">
-        <v>117.2</v>
+        <v>48.9</v>
       </c>
       <c r="D168" t="n">
-        <v>10736</v>
+        <v>16565</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>114.06</v>
+        <v>62.56</v>
       </c>
       <c r="B169" t="n">
-        <v>23844</v>
+        <v>22418</v>
       </c>
       <c r="C169" t="n">
-        <v>110.86</v>
+        <v>55.05</v>
       </c>
       <c r="D169" t="n">
-        <v>27555</v>
+        <v>21521</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>92.95999999999999</v>
+        <v>62.87</v>
       </c>
       <c r="B170" t="n">
-        <v>28879</v>
+        <v>21135</v>
       </c>
       <c r="C170" t="n">
-        <v>95.42</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="D170" t="n">
-        <v>18813</v>
+        <v>11448</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>94.40000000000001</v>
+        <v>63.21</v>
       </c>
       <c r="B171" t="n">
-        <v>33951</v>
+        <v>21689</v>
       </c>
       <c r="C171" t="n">
-        <v>91.64</v>
+        <v>57.99</v>
       </c>
       <c r="D171" t="n">
-        <v>21327</v>
+        <v>15656</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>91.45999999999999</v>
+        <v>63.73</v>
       </c>
       <c r="B172" t="n">
-        <v>24377</v>
+        <v>20568</v>
       </c>
       <c r="C172" t="n">
-        <v>92.98</v>
+        <v>58.1</v>
       </c>
       <c r="D172" t="n">
-        <v>15864</v>
+        <v>26213</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>94.56</v>
+        <v>63.91</v>
       </c>
       <c r="B173" t="n">
-        <v>33302</v>
+        <v>20063</v>
       </c>
       <c r="C173" t="n">
-        <v>91.78</v>
+        <v>57.6</v>
       </c>
       <c r="D173" t="n">
-        <v>26624</v>
+        <v>22944</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>100.4</v>
+        <v>64.06</v>
       </c>
       <c r="B174" t="n">
-        <v>46759</v>
+        <v>20548</v>
       </c>
       <c r="C174" t="n">
-        <v>101.94</v>
+        <v>56.05</v>
       </c>
       <c r="D174" t="n">
-        <v>19745</v>
+        <v>10735</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>95.62</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="B175" t="n">
-        <v>36844</v>
+        <v>19787</v>
       </c>
       <c r="C175" t="n">
-        <v>96.52</v>
+        <v>61.08</v>
       </c>
       <c r="D175" t="n">
-        <v>15636</v>
+        <v>11059</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>30.16</v>
+        <v>64.53</v>
       </c>
       <c r="B176" t="n">
-        <v>25140</v>
+        <v>20494</v>
       </c>
       <c r="C176" t="n">
-        <v>30.56</v>
+        <v>50.22</v>
       </c>
       <c r="D176" t="n">
-        <v>28365</v>
+        <v>15095</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>91.2</v>
+        <v>65.16</v>
       </c>
       <c r="B177" t="n">
-        <v>25526</v>
+        <v>22026</v>
       </c>
       <c r="C177" t="n">
-        <v>91.5</v>
+        <v>56.59</v>
       </c>
       <c r="D177" t="n">
-        <v>15244</v>
+        <v>23444</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>94.56999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="B178" t="n">
-        <v>33411</v>
+        <v>21564</v>
       </c>
       <c r="C178" t="n">
-        <v>96.34999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="D178" t="n">
-        <v>16592</v>
+        <v>28347</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>97.04000000000001</v>
+        <v>65.78</v>
       </c>
       <c r="B179" t="n">
-        <v>38235</v>
+        <v>21628</v>
       </c>
       <c r="C179" t="n">
-        <v>96.61</v>
+        <v>75.14</v>
       </c>
       <c r="D179" t="n">
-        <v>16264</v>
+        <v>23508</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>106.82</v>
+        <v>65.8</v>
       </c>
       <c r="B180" t="n">
-        <v>41500</v>
+        <v>21506</v>
       </c>
       <c r="C180" t="n">
-        <v>103</v>
+        <v>64.88</v>
       </c>
       <c r="D180" t="n">
-        <v>29256</v>
+        <v>25358</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>25.28</v>
+        <v>66.38</v>
       </c>
       <c r="B181" t="n">
-        <v>24359</v>
+        <v>18720</v>
       </c>
       <c r="C181" t="n">
-        <v>24.85</v>
+        <v>75.94</v>
       </c>
       <c r="D181" t="n">
-        <v>16301</v>
+        <v>25562</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>91.48</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="B182" t="n">
-        <v>24690</v>
+        <v>19170</v>
       </c>
       <c r="C182" t="n">
-        <v>94.48</v>
+        <v>54.07</v>
       </c>
       <c r="D182" t="n">
-        <v>15271</v>
+        <v>20248</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>105.98</v>
+        <v>68.23</v>
       </c>
       <c r="B183" t="n">
-        <v>45265</v>
+        <v>19597</v>
       </c>
       <c r="C183" t="n">
-        <v>105.62</v>
+        <v>56.68</v>
       </c>
       <c r="D183" t="n">
-        <v>27384</v>
+        <v>13528</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>96.52</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="B184" t="n">
-        <v>38840</v>
+        <v>19805</v>
       </c>
       <c r="C184" t="n">
-        <v>95.34999999999999</v>
+        <v>61.48</v>
       </c>
       <c r="D184" t="n">
-        <v>10003</v>
+        <v>13531</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126.38</v>
+        <v>68.61</v>
       </c>
       <c r="B185" t="n">
-        <v>25829</v>
+        <v>20425</v>
       </c>
       <c r="C185" t="n">
-        <v>125.04</v>
+        <v>63.88</v>
       </c>
       <c r="D185" t="n">
-        <v>10364</v>
+        <v>16138</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>93.95999999999999</v>
+        <v>68.61</v>
       </c>
       <c r="B186" t="n">
-        <v>33785</v>
+        <v>20004</v>
       </c>
       <c r="C186" t="n">
-        <v>96.23999999999999</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="D186" t="n">
-        <v>16651</v>
+        <v>26091</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>104.56</v>
+        <v>68.78</v>
       </c>
       <c r="B187" t="n">
-        <v>49215</v>
+        <v>20172</v>
       </c>
       <c r="C187" t="n">
-        <v>108.63</v>
+        <v>67.11</v>
       </c>
       <c r="D187" t="n">
-        <v>26562</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>90.88</v>
+        <v>68.89</v>
       </c>
       <c r="B188" t="n">
-        <v>25525</v>
+        <v>20879</v>
       </c>
       <c r="C188" t="n">
-        <v>94.54000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="D188" t="n">
-        <v>10825</v>
+        <v>16457</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>114.86</v>
+        <v>68.92</v>
       </c>
       <c r="B189" t="n">
-        <v>24204</v>
+        <v>20613</v>
       </c>
       <c r="C189" t="n">
-        <v>114.02</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D189" t="n">
-        <v>16792</v>
+        <v>15718</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>92.33</v>
+        <v>69.16</v>
       </c>
       <c r="B190" t="n">
-        <v>28255</v>
+        <v>20252</v>
       </c>
       <c r="C190" t="n">
-        <v>95.40000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="D190" t="n">
-        <v>21924</v>
+        <v>20622</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>23.14</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="B191" t="n">
-        <v>21488</v>
+        <v>20961</v>
       </c>
       <c r="C191" t="n">
-        <v>22.74</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="D191" t="n">
-        <v>16020</v>
+        <v>18834</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>112.91</v>
+        <v>69.31</v>
       </c>
       <c r="B192" t="n">
-        <v>27490</v>
+        <v>20031</v>
       </c>
       <c r="C192" t="n">
-        <v>115.55</v>
+        <v>67.34</v>
       </c>
       <c r="D192" t="n">
-        <v>22077</v>
+        <v>15843</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>103.55</v>
+        <v>69.47</v>
       </c>
       <c r="B193" t="n">
-        <v>51745</v>
+        <v>21299</v>
       </c>
       <c r="C193" t="n">
-        <v>104.31</v>
+        <v>53.66</v>
       </c>
       <c r="D193" t="n">
-        <v>28822</v>
+        <v>16275</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>99.02</v>
+        <v>70.31</v>
       </c>
       <c r="B194" t="n">
-        <v>41727</v>
+        <v>20696</v>
       </c>
       <c r="C194" t="n">
-        <v>102.43</v>
+        <v>56.79</v>
       </c>
       <c r="D194" t="n">
-        <v>16653</v>
+        <v>29280</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>109.21</v>
+        <v>70.63</v>
       </c>
       <c r="B195" t="n">
-        <v>35403</v>
+        <v>21170</v>
       </c>
       <c r="C195" t="n">
-        <v>113.4</v>
+        <v>84.38</v>
       </c>
       <c r="D195" t="n">
-        <v>18690</v>
+        <v>24865</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>99.12</v>
+        <v>70.94</v>
       </c>
       <c r="B196" t="n">
-        <v>40498</v>
+        <v>20193</v>
       </c>
       <c r="C196" t="n">
-        <v>102.48</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="D196" t="n">
-        <v>25585</v>
+        <v>18878</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>104.86</v>
+        <v>71.14</v>
       </c>
       <c r="B197" t="n">
-        <v>45409</v>
+        <v>19825</v>
       </c>
       <c r="C197" t="n">
-        <v>103.19</v>
+        <v>54.38</v>
       </c>
       <c r="D197" t="n">
-        <v>29274</v>
+        <v>24253</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>90.19</v>
+        <v>71.78</v>
       </c>
       <c r="B198" t="n">
-        <v>25784</v>
+        <v>20739</v>
       </c>
       <c r="C198" t="n">
-        <v>93.09999999999999</v>
+        <v>72.02</v>
       </c>
       <c r="D198" t="n">
-        <v>27892</v>
+        <v>21840</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>32.77</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="B199" t="n">
-        <v>24454</v>
+        <v>20534</v>
       </c>
       <c r="C199" t="n">
-        <v>32.17</v>
+        <v>85.89</v>
       </c>
       <c r="D199" t="n">
-        <v>11064</v>
+        <v>18896</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>96.75</v>
+        <v>72.17</v>
       </c>
       <c r="B200" t="n">
-        <v>40600</v>
+        <v>21825</v>
       </c>
       <c r="C200" t="n">
-        <v>98.66</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="D200" t="n">
-        <v>12132</v>
+        <v>21786</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>105.61</v>
+        <v>72.25</v>
       </c>
       <c r="B201" t="n">
-        <v>46072</v>
+        <v>19432</v>
       </c>
       <c r="C201" t="n">
-        <v>108.76</v>
+        <v>71.03</v>
       </c>
       <c r="D201" t="n">
-        <v>20755</v>
+        <v>26812</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>110.82</v>
+        <v>72.38</v>
       </c>
       <c r="B202" t="n">
-        <v>29884</v>
+        <v>20118</v>
       </c>
       <c r="C202" t="n">
-        <v>112.96</v>
+        <v>50.94</v>
       </c>
       <c r="D202" t="n">
-        <v>27645</v>
+        <v>28131</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>112.06</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="B203" t="n">
-        <v>27169</v>
+        <v>19400</v>
       </c>
       <c r="C203" t="n">
-        <v>110.18</v>
+        <v>68.48</v>
       </c>
       <c r="D203" t="n">
-        <v>28157</v>
+        <v>22206</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>159.05</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="B204" t="n">
-        <v>23217</v>
+        <v>20775</v>
       </c>
       <c r="C204" t="n">
-        <v>154.81</v>
+        <v>79.44</v>
       </c>
       <c r="D204" t="n">
-        <v>26572</v>
+        <v>20074</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>107.55</v>
+        <v>72.67</v>
       </c>
       <c r="B205" t="n">
-        <v>40208</v>
+        <v>21919</v>
       </c>
       <c r="C205" t="n">
-        <v>110.15</v>
+        <v>62.4</v>
       </c>
       <c r="D205" t="n">
-        <v>20979</v>
+        <v>25117</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>84.68000000000001</v>
+        <v>72.95</v>
       </c>
       <c r="B206" t="n">
-        <v>23794</v>
+        <v>20081</v>
       </c>
       <c r="C206" t="n">
-        <v>82.75</v>
+        <v>76.59</v>
       </c>
       <c r="D206" t="n">
-        <v>16284</v>
+        <v>20812</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>110.3</v>
+        <v>73.13</v>
       </c>
       <c r="B207" t="n">
-        <v>32465</v>
+        <v>21458</v>
       </c>
       <c r="C207" t="n">
-        <v>113.81</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="D207" t="n">
-        <v>16337</v>
+        <v>15773</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>92.64</v>
+        <v>73.22</v>
       </c>
       <c r="B208" t="n">
-        <v>29931</v>
+        <v>20722</v>
       </c>
       <c r="C208" t="n">
-        <v>95.12</v>
+        <v>73.88</v>
       </c>
       <c r="D208" t="n">
-        <v>19170</v>
+        <v>18184</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>108.44</v>
+        <v>73.36</v>
       </c>
       <c r="B209" t="n">
-        <v>35545</v>
+        <v>20841</v>
       </c>
       <c r="C209" t="n">
-        <v>111.98</v>
+        <v>66.58</v>
       </c>
       <c r="D209" t="n">
-        <v>10732</v>
+        <v>12785</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>91.69</v>
+        <v>73.5</v>
       </c>
       <c r="B210" t="n">
-        <v>26823</v>
+        <v>20649</v>
       </c>
       <c r="C210" t="n">
-        <v>91.48</v>
+        <v>74.45</v>
       </c>
       <c r="D210" t="n">
-        <v>10272</v>
+        <v>16747</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>101.85</v>
+        <v>73.89</v>
       </c>
       <c r="B211" t="n">
-        <v>44302</v>
+        <v>21266</v>
       </c>
       <c r="C211" t="n">
-        <v>105.23</v>
+        <v>77.72</v>
       </c>
       <c r="D211" t="n">
-        <v>15321</v>
+        <v>29777</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>108.89</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="B212" t="n">
-        <v>37075</v>
+        <v>21517</v>
       </c>
       <c r="C212" t="n">
-        <v>106.99</v>
+        <v>84.95</v>
       </c>
       <c r="D212" t="n">
-        <v>20618</v>
+        <v>16297</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>177.43</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="B213" t="n">
-        <v>23572</v>
+        <v>20632</v>
       </c>
       <c r="C213" t="n">
-        <v>174.81</v>
+        <v>62.28</v>
       </c>
       <c r="D213" t="n">
-        <v>20421</v>
+        <v>12861</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>90.55</v>
+        <v>74.45</v>
       </c>
       <c r="B214" t="n">
-        <v>24577</v>
+        <v>20266</v>
       </c>
       <c r="C214" t="n">
-        <v>88.06999999999999</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="D214" t="n">
-        <v>28559</v>
+        <v>13623</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>145.8</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="B215" t="n">
-        <v>25736</v>
+        <v>22249</v>
       </c>
       <c r="C215" t="n">
-        <v>149.13</v>
+        <v>64.3</v>
       </c>
       <c r="D215" t="n">
-        <v>25146</v>
+        <v>26168</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>112.82</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="B216" t="n">
-        <v>24501</v>
+        <v>20783</v>
       </c>
       <c r="C216" t="n">
-        <v>113.58</v>
+        <v>82.13</v>
       </c>
       <c r="D216" t="n">
-        <v>24978</v>
+        <v>29434</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>102.19</v>
+        <v>75.5</v>
       </c>
       <c r="B217" t="n">
-        <v>46693</v>
+        <v>20884</v>
       </c>
       <c r="C217" t="n">
-        <v>100.72</v>
+        <v>66.03</v>
       </c>
       <c r="D217" t="n">
-        <v>16965</v>
+        <v>14481</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>9.51</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="B218" t="n">
-        <v>22708</v>
+        <v>19899</v>
       </c>
       <c r="C218" t="n">
-        <v>9.81</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="D218" t="n">
-        <v>12508</v>
+        <v>10073</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>100.01</v>
+        <v>78.05</v>
       </c>
       <c r="B219" t="n">
-        <v>45250</v>
+        <v>20521</v>
       </c>
       <c r="C219" t="n">
-        <v>96.66</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="D219" t="n">
-        <v>20006</v>
+        <v>15481</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>109.53</v>
+        <v>78.31</v>
       </c>
       <c r="B220" t="n">
-        <v>35398</v>
+        <v>20085</v>
       </c>
       <c r="C220" t="n">
-        <v>106.36</v>
+        <v>66.89</v>
       </c>
       <c r="D220" t="n">
-        <v>26396</v>
+        <v>13031</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>103.17</v>
+        <v>78.64</v>
       </c>
       <c r="B221" t="n">
-        <v>48483</v>
+        <v>20749</v>
       </c>
       <c r="C221" t="n">
-        <v>99.72</v>
+        <v>72.83</v>
       </c>
       <c r="D221" t="n">
-        <v>17897</v>
+        <v>26780</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>105.98</v>
+        <v>78.92</v>
       </c>
       <c r="B222" t="n">
-        <v>42893</v>
+        <v>21190</v>
       </c>
       <c r="C222" t="n">
-        <v>107.07</v>
+        <v>66.52</v>
       </c>
       <c r="D222" t="n">
-        <v>11625</v>
+        <v>21039</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>108.04</v>
+        <v>78.94</v>
       </c>
       <c r="B223" t="n">
-        <v>40083</v>
+        <v>20854</v>
       </c>
       <c r="C223" t="n">
-        <v>104.95</v>
+        <v>75.19</v>
       </c>
       <c r="D223" t="n">
-        <v>23796</v>
+        <v>18867</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>93.09</v>
+        <v>79.02</v>
       </c>
       <c r="B224" t="n">
-        <v>28183</v>
+        <v>19801</v>
       </c>
       <c r="C224" t="n">
-        <v>95.84999999999999</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="D224" t="n">
-        <v>18212</v>
+        <v>19495</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>96.54000000000001</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="B225" t="n">
-        <v>36914</v>
+        <v>20192</v>
       </c>
       <c r="C225" t="n">
-        <v>100.66</v>
+        <v>94.78</v>
       </c>
       <c r="D225" t="n">
-        <v>15318</v>
+        <v>26830</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>114.67</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="B226" t="n">
-        <v>22720</v>
+        <v>20104</v>
       </c>
       <c r="C226" t="n">
-        <v>112.09</v>
+        <v>72.91</v>
       </c>
       <c r="D226" t="n">
-        <v>18494</v>
+        <v>10261</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>103.66</v>
+        <v>79.38</v>
       </c>
       <c r="B227" t="n">
-        <v>46006</v>
+        <v>19951</v>
       </c>
       <c r="C227" t="n">
-        <v>101.16</v>
+        <v>70.63</v>
       </c>
       <c r="D227" t="n">
-        <v>23167</v>
+        <v>29569</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>98.22</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="B228" t="n">
-        <v>41375</v>
+        <v>20919</v>
       </c>
       <c r="C228" t="n">
-        <v>94.20999999999999</v>
+        <v>65.25</v>
       </c>
       <c r="D228" t="n">
-        <v>27094</v>
+        <v>21673</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>90.26000000000001</v>
+        <v>80.03</v>
       </c>
       <c r="B229" t="n">
-        <v>24285</v>
+        <v>20169</v>
       </c>
       <c r="C229" t="n">
-        <v>91.06</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="D229" t="n">
-        <v>22150</v>
+        <v>18718</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>78.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="B230" t="n">
-        <v>24743</v>
+        <v>20599</v>
       </c>
       <c r="C230" t="n">
-        <v>81.31</v>
+        <v>64.89</v>
       </c>
       <c r="D230" t="n">
-        <v>28107</v>
+        <v>12946</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>97.94</v>
+        <v>80.84</v>
       </c>
       <c r="B231" t="n">
-        <v>42882</v>
+        <v>20624</v>
       </c>
       <c r="C231" t="n">
-        <v>98.40000000000001</v>
+        <v>75.59</v>
       </c>
       <c r="D231" t="n">
-        <v>18329</v>
+        <v>28561</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>102.4</v>
+        <v>81.16</v>
       </c>
       <c r="B232" t="n">
-        <v>44563</v>
+        <v>21128</v>
       </c>
       <c r="C232" t="n">
-        <v>98.98999999999999</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="D232" t="n">
-        <v>10163</v>
+        <v>14517</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>94.53</v>
+        <v>81.2</v>
       </c>
       <c r="B233" t="n">
-        <v>33749</v>
+        <v>19944</v>
       </c>
       <c r="C233" t="n">
-        <v>94.72</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="D233" t="n">
-        <v>16127</v>
+        <v>29902</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>114.53</v>
+        <v>81.38</v>
       </c>
       <c r="B234" t="n">
-        <v>23345</v>
+        <v>21487</v>
       </c>
       <c r="C234" t="n">
-        <v>115.95</v>
+        <v>72</v>
       </c>
       <c r="D234" t="n">
-        <v>10169</v>
+        <v>23753</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>105.63</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="B235" t="n">
-        <v>43478</v>
+        <v>20737</v>
       </c>
       <c r="C235" t="n">
-        <v>107.81</v>
+        <v>95.08</v>
       </c>
       <c r="D235" t="n">
-        <v>14326</v>
+        <v>11258</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>94.26000000000001</v>
+        <v>81.75</v>
       </c>
       <c r="B236" t="n">
-        <v>31786</v>
+        <v>20597</v>
       </c>
       <c r="C236" t="n">
-        <v>91.04000000000001</v>
+        <v>74.37</v>
       </c>
       <c r="D236" t="n">
-        <v>28531</v>
+        <v>25088</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>22.64</v>
+        <v>82.17</v>
       </c>
       <c r="B237" t="n">
-        <v>25537</v>
+        <v>20360</v>
       </c>
       <c r="C237" t="n">
-        <v>23.3</v>
+        <v>77.88</v>
       </c>
       <c r="D237" t="n">
-        <v>19036</v>
+        <v>25750</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>91.43000000000001</v>
+        <v>82.56</v>
       </c>
       <c r="B238" t="n">
-        <v>24889</v>
+        <v>20769</v>
       </c>
       <c r="C238" t="n">
-        <v>92.40000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="D238" t="n">
-        <v>15222</v>
+        <v>10359</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>103.64</v>
+        <v>83.23</v>
       </c>
       <c r="B239" t="n">
-        <v>46900</v>
+        <v>19907</v>
       </c>
       <c r="C239" t="n">
-        <v>105.57</v>
+        <v>91.95</v>
       </c>
       <c r="D239" t="n">
-        <v>25833</v>
+        <v>16335</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>106.01</v>
+        <v>83.48</v>
       </c>
       <c r="B240" t="n">
-        <v>46647</v>
+        <v>20334</v>
       </c>
       <c r="C240" t="n">
-        <v>105.89</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="D240" t="n">
-        <v>12820</v>
+        <v>29983</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>96.45999999999999</v>
+        <v>84.12</v>
       </c>
       <c r="B241" t="n">
-        <v>35895</v>
+        <v>20428</v>
       </c>
       <c r="C241" t="n">
-        <v>97.73</v>
+        <v>93.89</v>
       </c>
       <c r="D241" t="n">
-        <v>11390</v>
+        <v>17436</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>114.99</v>
+        <v>84.53</v>
       </c>
       <c r="B242" t="n">
-        <v>23189</v>
+        <v>19971</v>
       </c>
       <c r="C242" t="n">
-        <v>114.84</v>
+        <v>82.47</v>
       </c>
       <c r="D242" t="n">
-        <v>13141</v>
+        <v>15300</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>114.07</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="B243" t="n">
-        <v>23657</v>
+        <v>20501</v>
       </c>
       <c r="C243" t="n">
-        <v>109.05</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="D243" t="n">
-        <v>25460</v>
+        <v>17983</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>108.95</v>
+        <v>85.2</v>
       </c>
       <c r="B244" t="n">
-        <v>34379</v>
+        <v>20208</v>
       </c>
       <c r="C244" t="n">
-        <v>112.01</v>
+        <v>92.48</v>
       </c>
       <c r="D244" t="n">
-        <v>21613</v>
+        <v>24542</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>105.61</v>
+        <v>85.28</v>
       </c>
       <c r="B245" t="n">
-        <v>42392</v>
+        <v>20184</v>
       </c>
       <c r="C245" t="n">
-        <v>108.27</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="D245" t="n">
-        <v>17314</v>
+        <v>27301</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>94.44</v>
+        <v>85.34</v>
       </c>
       <c r="B246" t="n">
-        <v>34465</v>
+        <v>21163</v>
       </c>
       <c r="C246" t="n">
-        <v>95.55</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D246" t="n">
-        <v>25941</v>
+        <v>20001</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>105.9</v>
+        <v>85.73</v>
       </c>
       <c r="B247" t="n">
-        <v>44477</v>
+        <v>19737</v>
       </c>
       <c r="C247" t="n">
-        <v>108.01</v>
+        <v>68.3</v>
       </c>
       <c r="D247" t="n">
-        <v>21911</v>
+        <v>16313</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>104.57</v>
+        <v>86.09</v>
       </c>
       <c r="B248" t="n">
-        <v>45247</v>
+        <v>20114</v>
       </c>
       <c r="C248" t="n">
-        <v>106.39</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="D248" t="n">
-        <v>29368</v>
+        <v>11590</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>97.23999999999999</v>
+        <v>86.19</v>
       </c>
       <c r="B249" t="n">
-        <v>41540</v>
+        <v>21232</v>
       </c>
       <c r="C249" t="n">
-        <v>97.67</v>
+        <v>96.78</v>
       </c>
       <c r="D249" t="n">
-        <v>15911</v>
+        <v>22842</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="B250" t="n">
+        <v>20257</v>
+      </c>
+      <c r="C250" t="n">
         <v>106.78</v>
       </c>
-      <c r="B250" t="n">
-        <v>44343</v>
-      </c>
-      <c r="C250" t="n">
-        <v>105.94</v>
-      </c>
       <c r="D250" t="n">
-        <v>24969</v>
+        <v>28219</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>179.5</v>
+        <v>87.42</v>
       </c>
       <c r="B251" t="n">
-        <v>23065</v>
+        <v>20113</v>
       </c>
       <c r="C251" t="n">
-        <v>180</v>
+        <v>111.17</v>
       </c>
       <c r="D251" t="n">
-        <v>21484</v>
+        <v>13411</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>133.37</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="B252" t="n">
-        <v>24187</v>
+        <v>20735</v>
       </c>
       <c r="C252" t="n">
-        <v>129.31</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="D252" t="n">
-        <v>23019</v>
+        <v>15560</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>146.43</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="B253" t="n">
-        <v>22686</v>
+        <v>20870</v>
       </c>
       <c r="C253" t="n">
-        <v>145.69</v>
+        <v>72.91</v>
       </c>
       <c r="D253" t="n">
-        <v>14596</v>
+        <v>20781</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>96.15000000000001</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="B254" t="n">
-        <v>36558</v>
+        <v>19681</v>
       </c>
       <c r="C254" t="n">
-        <v>93.98999999999999</v>
+        <v>72.52</v>
       </c>
       <c r="D254" t="n">
-        <v>28309</v>
+        <v>13905</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>107.69</v>
+        <v>88.22</v>
       </c>
       <c r="B255" t="n">
-        <v>39636</v>
+        <v>20396</v>
       </c>
       <c r="C255" t="n">
-        <v>105.66</v>
+        <v>81.3</v>
       </c>
       <c r="D255" t="n">
-        <v>14591</v>
+        <v>12724</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>106.69</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="B256" t="n">
-        <v>42119</v>
+        <v>20247</v>
       </c>
       <c r="C256" t="n">
-        <v>102.72</v>
+        <v>78.55</v>
       </c>
       <c r="D256" t="n">
-        <v>25451</v>
+        <v>10933</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>172.23</v>
+        <v>88.84</v>
       </c>
       <c r="B257" t="n">
-        <v>22973</v>
+        <v>20221</v>
       </c>
       <c r="C257" t="n">
-        <v>177.37</v>
+        <v>72.09</v>
       </c>
       <c r="D257" t="n">
-        <v>14045</v>
+        <v>25449</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>122.17</v>
+        <v>89.06</v>
       </c>
       <c r="B258" t="n">
-        <v>23714</v>
+        <v>20992</v>
       </c>
       <c r="C258" t="n">
-        <v>120.02</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="D258" t="n">
-        <v>11224</v>
+        <v>12461</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>110.49</v>
+        <v>89.25</v>
       </c>
       <c r="B259" t="n">
-        <v>31254</v>
+        <v>20114</v>
       </c>
       <c r="C259" t="n">
-        <v>106.61</v>
+        <v>82.98</v>
       </c>
       <c r="D259" t="n">
-        <v>17369</v>
+        <v>28920</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>93.81</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="B260" t="n">
-        <v>29613</v>
+        <v>21373</v>
       </c>
       <c r="C260" t="n">
-        <v>93.20999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="D260" t="n">
-        <v>13553</v>
+        <v>24377</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>96.45</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="B261" t="n">
-        <v>37489</v>
+        <v>21256</v>
       </c>
       <c r="C261" t="n">
-        <v>94.81</v>
+        <v>75.36</v>
       </c>
       <c r="D261" t="n">
-        <v>27982</v>
+        <v>28508</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>96.84999999999999</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="B262" t="n">
-        <v>36709</v>
+        <v>20450</v>
       </c>
       <c r="C262" t="n">
-        <v>92.91</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="D262" t="n">
-        <v>29833</v>
+        <v>11837</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>109.63</v>
+        <v>90.58</v>
       </c>
       <c r="B263" t="n">
-        <v>33642</v>
+        <v>20754</v>
       </c>
       <c r="C263" t="n">
-        <v>109.97</v>
+        <v>96.42</v>
       </c>
       <c r="D263" t="n">
-        <v>10436</v>
+        <v>29430</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>97.11</v>
+        <v>90.8</v>
       </c>
       <c r="B264" t="n">
-        <v>34888</v>
+        <v>20896</v>
       </c>
       <c r="C264" t="n">
-        <v>100.11</v>
+        <v>102.45</v>
       </c>
       <c r="D264" t="n">
-        <v>29375</v>
+        <v>26087</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>160.99</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="B265" t="n">
-        <v>21618</v>
+        <v>21779</v>
       </c>
       <c r="C265" t="n">
-        <v>157.23</v>
+        <v>84.77</v>
       </c>
       <c r="D265" t="n">
-        <v>22140</v>
+        <v>18762</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>98</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="B266" t="n">
-        <v>39682</v>
+        <v>21581</v>
       </c>
       <c r="C266" t="n">
-        <v>98.8</v>
+        <v>101.39</v>
       </c>
       <c r="D266" t="n">
-        <v>16258</v>
+        <v>17261</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>113.46</v>
+        <v>92.23</v>
       </c>
       <c r="B267" t="n">
-        <v>26923</v>
+        <v>22030</v>
       </c>
       <c r="C267" t="n">
-        <v>114.04</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="D267" t="n">
-        <v>25791</v>
+        <v>13182</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>96.34999999999999</v>
+        <v>92.28</v>
       </c>
       <c r="B268" t="n">
-        <v>38359</v>
+        <v>22827</v>
       </c>
       <c r="C268" t="n">
-        <v>95.92</v>
+        <v>87.03</v>
       </c>
       <c r="D268" t="n">
-        <v>24846</v>
+        <v>16570</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>93.79000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="B269" t="n">
-        <v>31706</v>
+        <v>22369</v>
       </c>
       <c r="C269" t="n">
-        <v>96.42</v>
+        <v>78.5</v>
       </c>
       <c r="D269" t="n">
-        <v>18730</v>
+        <v>23357</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>100.74</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="B270" t="n">
-        <v>44613</v>
+        <v>22690</v>
       </c>
       <c r="C270" t="n">
-        <v>102.25</v>
+        <v>89</v>
       </c>
       <c r="D270" t="n">
-        <v>18251</v>
+        <v>26269</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>108.93</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="B271" t="n">
-        <v>37860</v>
+        <v>22641</v>
       </c>
       <c r="C271" t="n">
-        <v>107.79</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="D271" t="n">
-        <v>10221</v>
+        <v>10166</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>91.55</v>
+        <v>93.52</v>
       </c>
       <c r="B272" t="n">
-        <v>25141</v>
+        <v>23810</v>
       </c>
       <c r="C272" t="n">
-        <v>94.95999999999999</v>
+        <v>80.88</v>
       </c>
       <c r="D272" t="n">
-        <v>24604</v>
+        <v>18615</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>106.63</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="B273" t="n">
-        <v>42821</v>
+        <v>23744</v>
       </c>
       <c r="C273" t="n">
-        <v>102.61</v>
+        <v>88.98</v>
       </c>
       <c r="D273" t="n">
-        <v>13102</v>
+        <v>10011</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>105.46</v>
+        <v>93.67</v>
       </c>
       <c r="B274" t="n">
-        <v>45660</v>
+        <v>22787</v>
       </c>
       <c r="C274" t="n">
-        <v>105.35</v>
+        <v>113.07</v>
       </c>
       <c r="D274" t="n">
-        <v>13527</v>
+        <v>14150</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>99.36</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="B275" t="n">
-        <v>43423</v>
+        <v>24178</v>
       </c>
       <c r="C275" t="n">
-        <v>102.33</v>
+        <v>94.38</v>
       </c>
       <c r="D275" t="n">
-        <v>27752</v>
+        <v>11014</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>114.71</v>
+        <v>95.45</v>
       </c>
       <c r="B276" t="n">
-        <v>25210</v>
+        <v>26039</v>
       </c>
       <c r="C276" t="n">
-        <v>116.57</v>
+        <v>88.91</v>
       </c>
       <c r="D276" t="n">
-        <v>23486</v>
+        <v>19630</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>106.67</v>
+        <v>96.02</v>
       </c>
       <c r="B277" t="n">
-        <v>42355</v>
+        <v>27470</v>
       </c>
       <c r="C277" t="n">
-        <v>105.81</v>
+        <v>108.18</v>
       </c>
       <c r="D277" t="n">
-        <v>10546</v>
+        <v>21298</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>99.3</v>
+        <v>96.05</v>
       </c>
       <c r="B278" t="n">
-        <v>43904</v>
+        <v>25880</v>
       </c>
       <c r="C278" t="n">
-        <v>96.84</v>
+        <v>97.8</v>
       </c>
       <c r="D278" t="n">
-        <v>17313</v>
+        <v>25773</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>108.33</v>
+        <v>96.33</v>
       </c>
       <c r="B279" t="n">
-        <v>38360</v>
+        <v>27617</v>
       </c>
       <c r="C279" t="n">
-        <v>109.91</v>
+        <v>99.02</v>
       </c>
       <c r="D279" t="n">
-        <v>22309</v>
+        <v>19810</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>96.59</v>
+        <v>96.63</v>
       </c>
       <c r="B280" t="n">
-        <v>35899</v>
+        <v>27958</v>
       </c>
       <c r="C280" t="n">
-        <v>93.33</v>
+        <v>92.34</v>
       </c>
       <c r="D280" t="n">
-        <v>23696</v>
+        <v>29596</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>95</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="B281" t="n">
-        <v>32765</v>
+        <v>32082</v>
       </c>
       <c r="C281" t="n">
-        <v>92.18000000000001</v>
+        <v>101.4</v>
       </c>
       <c r="D281" t="n">
-        <v>20541</v>
+        <v>18936</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>95.59</v>
+        <v>98.17</v>
       </c>
       <c r="B282" t="n">
-        <v>34067</v>
+        <v>32401</v>
       </c>
       <c r="C282" t="n">
-        <v>94.98999999999999</v>
+        <v>107.65</v>
       </c>
       <c r="D282" t="n">
-        <v>10281</v>
+        <v>28299</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>109.8</v>
+        <v>98.34</v>
       </c>
       <c r="B283" t="n">
-        <v>33351</v>
+        <v>31187</v>
       </c>
       <c r="C283" t="n">
-        <v>112.2</v>
+        <v>110.61</v>
       </c>
       <c r="D283" t="n">
-        <v>11852</v>
+        <v>27713</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>93.38</v>
+        <v>98.73</v>
       </c>
       <c r="B284" t="n">
-        <v>30479</v>
+        <v>31984</v>
       </c>
       <c r="C284" t="n">
-        <v>95.73</v>
+        <v>111.92</v>
       </c>
       <c r="D284" t="n">
-        <v>13553</v>
+        <v>10576</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>54.4</v>
+        <v>98.92</v>
       </c>
       <c r="B285" t="n">
-        <v>23582</v>
+        <v>33050</v>
       </c>
       <c r="C285" t="n">
-        <v>53.48</v>
+        <v>118.61</v>
       </c>
       <c r="D285" t="n">
-        <v>24260</v>
+        <v>22039</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>58.2</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="B286" t="n">
-        <v>23444</v>
+        <v>32220</v>
       </c>
       <c r="C286" t="n">
-        <v>59.97</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D286" t="n">
-        <v>11664</v>
+        <v>22587</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>93</v>
+        <v>99.66</v>
       </c>
       <c r="B287" t="n">
-        <v>27637</v>
+        <v>34277</v>
       </c>
       <c r="C287" t="n">
-        <v>89.3</v>
+        <v>125.03</v>
       </c>
       <c r="D287" t="n">
-        <v>21299</v>
+        <v>10473</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>110.2</v>
+        <v>100.02</v>
       </c>
       <c r="B288" t="n">
-        <v>30096</v>
+        <v>35381</v>
       </c>
       <c r="C288" t="n">
-        <v>109.28</v>
+        <v>119.63</v>
       </c>
       <c r="D288" t="n">
-        <v>12899</v>
+        <v>15432</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>92.73999999999999</v>
+        <v>100.73</v>
       </c>
       <c r="B289" t="n">
-        <v>27391</v>
+        <v>37616</v>
       </c>
       <c r="C289" t="n">
-        <v>94.98999999999999</v>
+        <v>90.72</v>
       </c>
       <c r="D289" t="n">
-        <v>22516</v>
+        <v>27624</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>107.76</v>
+        <v>100.87</v>
       </c>
       <c r="B290" t="n">
-        <v>40677</v>
+        <v>36599</v>
       </c>
       <c r="C290" t="n">
-        <v>109.86</v>
+        <v>86.33</v>
       </c>
       <c r="D290" t="n">
-        <v>24641</v>
+        <v>20359</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>13.02</v>
+        <v>101.17</v>
       </c>
       <c r="B291" t="n">
-        <v>24060</v>
+        <v>37148</v>
       </c>
       <c r="C291" t="n">
-        <v>12.85</v>
+        <v>95.66</v>
       </c>
       <c r="D291" t="n">
-        <v>11053</v>
+        <v>25297</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>99.19</v>
+        <v>101.4</v>
       </c>
       <c r="B292" t="n">
-        <v>42664</v>
+        <v>37054</v>
       </c>
       <c r="C292" t="n">
-        <v>99.52</v>
+        <v>87.98</v>
       </c>
       <c r="D292" t="n">
-        <v>13329</v>
+        <v>17002</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>107.35</v>
+        <v>101.63</v>
       </c>
       <c r="B293" t="n">
-        <v>40305</v>
+        <v>37272</v>
       </c>
       <c r="C293" t="n">
-        <v>107.35</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="D293" t="n">
-        <v>21085</v>
+        <v>13730</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>113.77</v>
+        <v>101.75</v>
       </c>
       <c r="B294" t="n">
-        <v>25678</v>
+        <v>38196</v>
       </c>
       <c r="C294" t="n">
-        <v>113.35</v>
+        <v>124.66</v>
       </c>
       <c r="D294" t="n">
-        <v>10801</v>
+        <v>26597</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>94.86</v>
+        <v>101.92</v>
       </c>
       <c r="B295" t="n">
-        <v>33494</v>
+        <v>36045</v>
       </c>
       <c r="C295" t="n">
-        <v>93.54000000000001</v>
+        <v>95.97</v>
       </c>
       <c r="D295" t="n">
-        <v>14347</v>
+        <v>15949</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>93.47</v>
+        <v>102.24</v>
       </c>
       <c r="B296" t="n">
-        <v>27944</v>
+        <v>37040</v>
       </c>
       <c r="C296" t="n">
-        <v>93.12</v>
+        <v>94.48</v>
       </c>
       <c r="D296" t="n">
-        <v>14149</v>
+        <v>12360</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>107.08</v>
+        <v>102.3</v>
       </c>
       <c r="B297" t="n">
-        <v>41212</v>
+        <v>38172</v>
       </c>
       <c r="C297" t="n">
-        <v>109.84</v>
+        <v>94.58</v>
       </c>
       <c r="D297" t="n">
-        <v>11603</v>
+        <v>27652</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>106.18</v>
+        <v>102.57</v>
       </c>
       <c r="B298" t="n">
-        <v>44147</v>
+        <v>36887</v>
       </c>
       <c r="C298" t="n">
-        <v>107.94</v>
+        <v>109.92</v>
       </c>
       <c r="D298" t="n">
-        <v>12836</v>
+        <v>20914</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>100.08</v>
+        <v>102.64</v>
       </c>
       <c r="B299" t="n">
-        <v>44634</v>
+        <v>37198</v>
       </c>
       <c r="C299" t="n">
-        <v>102.84</v>
+        <v>103.09</v>
       </c>
       <c r="D299" t="n">
-        <v>12684</v>
+        <v>20615</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>102.89</v>
+        <v>103.81</v>
       </c>
       <c r="B300" t="n">
-        <v>46186</v>
+        <v>37246</v>
       </c>
       <c r="C300" t="n">
-        <v>100.25</v>
+        <v>85.92</v>
       </c>
       <c r="D300" t="n">
-        <v>25643</v>
+        <v>27193</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>90.84999999999999</v>
+        <v>104.37</v>
       </c>
       <c r="B301" t="n">
-        <v>20257</v>
+        <v>37046</v>
       </c>
       <c r="C301" t="n">
-        <v>89.19</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="D301" t="n">
-        <v>12792</v>
+        <v>18454</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>135.16</v>
+        <v>104.85</v>
       </c>
       <c r="B302" t="n">
-        <v>23305</v>
+        <v>38135</v>
       </c>
       <c r="C302" t="n">
-        <v>134.57</v>
+        <v>93</v>
       </c>
       <c r="D302" t="n">
-        <v>16718</v>
+        <v>12196</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>97.84999999999999</v>
+        <v>105.19</v>
       </c>
       <c r="B303" t="n">
-        <v>41150</v>
+        <v>37064</v>
       </c>
       <c r="C303" t="n">
-        <v>99.56</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="D303" t="n">
-        <v>24495</v>
+        <v>25035</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>91.16</v>
+        <v>105.31</v>
       </c>
       <c r="B304" t="n">
-        <v>25403</v>
+        <v>35471</v>
       </c>
       <c r="C304" t="n">
-        <v>87.3</v>
+        <v>107.83</v>
       </c>
       <c r="D304" t="n">
-        <v>17848</v>
+        <v>15357</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>114.15</v>
+        <v>105.95</v>
       </c>
       <c r="B305" t="n">
-        <v>23017</v>
+        <v>34225</v>
       </c>
       <c r="C305" t="n">
-        <v>110.5</v>
+        <v>88.95</v>
       </c>
       <c r="D305" t="n">
-        <v>23200</v>
+        <v>13951</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>112.09</v>
+        <v>105.96</v>
       </c>
       <c r="B306" t="n">
-        <v>27127</v>
+        <v>35414</v>
       </c>
       <c r="C306" t="n">
-        <v>113.07</v>
+        <v>122.1</v>
       </c>
       <c r="D306" t="n">
-        <v>20400</v>
+        <v>29482</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>100.42</v>
+        <v>106.62</v>
       </c>
       <c r="B307" t="n">
-        <v>43808</v>
+        <v>34293</v>
       </c>
       <c r="C307" t="n">
-        <v>98.72</v>
+        <v>101.03</v>
       </c>
       <c r="D307" t="n">
-        <v>11552</v>
+        <v>21951</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>105.6</v>
+        <v>106.64</v>
       </c>
       <c r="B308" t="n">
-        <v>45500</v>
+        <v>33318</v>
       </c>
       <c r="C308" t="n">
-        <v>102.14</v>
+        <v>102.7</v>
       </c>
       <c r="D308" t="n">
-        <v>15521</v>
+        <v>17193</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>42.29</v>
+        <v>107.61</v>
       </c>
       <c r="B309" t="n">
-        <v>25194</v>
+        <v>30737</v>
       </c>
       <c r="C309" t="n">
-        <v>43.96</v>
+        <v>107.79</v>
       </c>
       <c r="D309" t="n">
-        <v>25158</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>99.89</v>
+        <v>107.68</v>
       </c>
       <c r="B310" t="n">
-        <v>45692</v>
+        <v>30892</v>
       </c>
       <c r="C310" t="n">
-        <v>100.7</v>
+        <v>126.49</v>
       </c>
       <c r="D310" t="n">
-        <v>27638</v>
+        <v>21685</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>113.59</v>
+        <v>108.01</v>
       </c>
       <c r="B311" t="n">
-        <v>26679</v>
+        <v>30939</v>
       </c>
       <c r="C311" t="n">
-        <v>113.3</v>
+        <v>123.87</v>
       </c>
       <c r="D311" t="n">
-        <v>18956</v>
+        <v>11570</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>132.5</v>
+        <v>108.69</v>
       </c>
       <c r="B312" t="n">
-        <v>24851</v>
+        <v>28035</v>
       </c>
       <c r="C312" t="n">
-        <v>131.84</v>
+        <v>106.53</v>
       </c>
       <c r="D312" t="n">
-        <v>17024</v>
+        <v>18367</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>96.23999999999999</v>
+        <v>108.99</v>
       </c>
       <c r="B313" t="n">
-        <v>35716</v>
+        <v>28569</v>
       </c>
       <c r="C313" t="n">
-        <v>93</v>
+        <v>81.58</v>
       </c>
       <c r="D313" t="n">
-        <v>13067</v>
+        <v>26561</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>113.34</v>
+        <v>109.07</v>
       </c>
       <c r="B314" t="n">
-        <v>25712</v>
+        <v>27738</v>
       </c>
       <c r="C314" t="n">
-        <v>117.07</v>
+        <v>107.23</v>
       </c>
       <c r="D314" t="n">
-        <v>27846</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>102.86</v>
+        <v>109.21</v>
       </c>
       <c r="B315" t="n">
-        <v>47986</v>
+        <v>30363</v>
       </c>
       <c r="C315" t="n">
-        <v>100.17</v>
+        <v>100.73</v>
       </c>
       <c r="D315" t="n">
-        <v>14450</v>
+        <v>24872</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>112.4</v>
+        <v>109.31</v>
       </c>
       <c r="B316" t="n">
-        <v>26028</v>
+        <v>27714</v>
       </c>
       <c r="C316" t="n">
-        <v>116</v>
+        <v>112.59</v>
       </c>
       <c r="D316" t="n">
-        <v>20530</v>
+        <v>28605</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>90.56999999999999</v>
+        <v>109.42</v>
       </c>
       <c r="B317" t="n">
-        <v>21006</v>
+        <v>27572</v>
       </c>
       <c r="C317" t="n">
-        <v>87.58</v>
+        <v>107.23</v>
       </c>
       <c r="D317" t="n">
-        <v>26268</v>
+        <v>21904</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>99.47</v>
+        <v>111.24</v>
       </c>
       <c r="B318" t="n">
-        <v>43177</v>
+        <v>24884</v>
       </c>
       <c r="C318" t="n">
-        <v>97.61</v>
+        <v>121.09</v>
       </c>
       <c r="D318" t="n">
-        <v>29699</v>
+        <v>13448</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>95.14</v>
+        <v>111.26</v>
       </c>
       <c r="B319" t="n">
-        <v>34525</v>
+        <v>24536</v>
       </c>
       <c r="C319" t="n">
-        <v>95.01000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="D319" t="n">
-        <v>26442</v>
+        <v>14045</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>100.66</v>
+        <v>111.78</v>
       </c>
       <c r="B320" t="n">
-        <v>47779</v>
+        <v>23450</v>
       </c>
       <c r="C320" t="n">
-        <v>100.4</v>
+        <v>95.16</v>
       </c>
       <c r="D320" t="n">
-        <v>21211</v>
+        <v>28565</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>90.31</v>
+        <v>112.01</v>
       </c>
       <c r="B321" t="n">
-        <v>25823</v>
+        <v>24497</v>
       </c>
       <c r="C321" t="n">
-        <v>91.81</v>
+        <v>113.67</v>
       </c>
       <c r="D321" t="n">
-        <v>11908</v>
+        <v>25122</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>99.75</v>
+        <v>112.57</v>
       </c>
       <c r="B322" t="n">
-        <v>43320</v>
+        <v>22622</v>
       </c>
       <c r="C322" t="n">
-        <v>102.15</v>
+        <v>110.65</v>
       </c>
       <c r="D322" t="n">
-        <v>25236</v>
+        <v>15279</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>96.72</v>
+        <v>112.58</v>
       </c>
       <c r="B323" t="n">
-        <v>38684</v>
+        <v>22994</v>
       </c>
       <c r="C323" t="n">
-        <v>97.7</v>
+        <v>88.91</v>
       </c>
       <c r="D323" t="n">
-        <v>22544</v>
+        <v>24831</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>91.92</v>
+        <v>113.9</v>
       </c>
       <c r="B324" t="n">
-        <v>27553</v>
+        <v>21408</v>
       </c>
       <c r="C324" t="n">
-        <v>88.76000000000001</v>
+        <v>126.18</v>
       </c>
       <c r="D324" t="n">
-        <v>26552</v>
+        <v>18819</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>104.7</v>
+        <v>114.57</v>
       </c>
       <c r="B325" t="n">
-        <v>47966</v>
+        <v>20305</v>
       </c>
       <c r="C325" t="n">
-        <v>106.84</v>
+        <v>110.29</v>
       </c>
       <c r="D325" t="n">
-        <v>29735</v>
+        <v>21067</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>101.66</v>
+        <v>114.76</v>
       </c>
       <c r="B326" t="n">
-        <v>44934</v>
+        <v>20477</v>
       </c>
       <c r="C326" t="n">
-        <v>100.67</v>
+        <v>110.25</v>
       </c>
       <c r="D326" t="n">
-        <v>17662</v>
+        <v>25044</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>0.01</v>
+        <v>115.33</v>
       </c>
       <c r="B327" t="n">
-        <v>21265</v>
+        <v>20538</v>
       </c>
       <c r="C327" t="n">
-        <v>0</v>
+        <v>113.5</v>
       </c>
       <c r="D327" t="n">
-        <v>15098</v>
+        <v>22522</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>92.03</v>
+        <v>116.39</v>
       </c>
       <c r="B328" t="n">
-        <v>25591</v>
+        <v>20980</v>
       </c>
       <c r="C328" t="n">
-        <v>92.06999999999999</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="D328" t="n">
-        <v>13373</v>
+        <v>20203</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>131.93</v>
+        <v>116.77</v>
       </c>
       <c r="B329" t="n">
-        <v>22765</v>
+        <v>21126</v>
       </c>
       <c r="C329" t="n">
-        <v>132.73</v>
+        <v>123.7</v>
       </c>
       <c r="D329" t="n">
-        <v>23528</v>
+        <v>28667</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>91.89</v>
+        <v>116.96</v>
       </c>
       <c r="B330" t="n">
-        <v>23765</v>
+        <v>21392</v>
       </c>
       <c r="C330" t="n">
-        <v>89.39</v>
+        <v>115.01</v>
       </c>
       <c r="D330" t="n">
-        <v>22492</v>
+        <v>21945</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>8.02</v>
+        <v>117.54</v>
       </c>
       <c r="B331" t="n">
-        <v>22337</v>
+        <v>18447</v>
       </c>
       <c r="C331" t="n">
-        <v>8.66</v>
+        <v>109.3</v>
       </c>
       <c r="D331" t="n">
-        <v>22005</v>
+        <v>28899</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>55.44</v>
+        <v>117.57</v>
       </c>
       <c r="B332" t="n">
-        <v>22427</v>
+        <v>19549</v>
       </c>
       <c r="C332" t="n">
-        <v>54.42</v>
+        <v>97.44</v>
       </c>
       <c r="D332" t="n">
-        <v>29979</v>
+        <v>13748</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>141.57</v>
+        <v>118.45</v>
       </c>
       <c r="B333" t="n">
-        <v>25549</v>
+        <v>20217</v>
       </c>
       <c r="C333" t="n">
-        <v>136.54</v>
+        <v>109.83</v>
       </c>
       <c r="D333" t="n">
-        <v>13574</v>
+        <v>17358</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>90.28</v>
+        <v>118.99</v>
       </c>
       <c r="B334" t="n">
-        <v>24800</v>
+        <v>19846</v>
       </c>
       <c r="C334" t="n">
-        <v>92.81999999999999</v>
+        <v>105.33</v>
       </c>
       <c r="D334" t="n">
-        <v>29527</v>
+        <v>29960</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>97.19</v>
+        <v>119.09</v>
       </c>
       <c r="B335" t="n">
-        <v>40100</v>
+        <v>19534</v>
       </c>
       <c r="C335" t="n">
-        <v>98.56</v>
+        <v>119.84</v>
       </c>
       <c r="D335" t="n">
-        <v>28441</v>
+        <v>29337</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>101.89</v>
+        <v>119.18</v>
       </c>
       <c r="B336" t="n">
-        <v>46754</v>
+        <v>19430</v>
       </c>
       <c r="C336" t="n">
-        <v>102.21</v>
+        <v>109.7</v>
       </c>
       <c r="D336" t="n">
-        <v>16599</v>
+        <v>22236</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>95.84</v>
+        <v>120</v>
       </c>
       <c r="B337" t="n">
-        <v>34665</v>
+        <v>19757</v>
       </c>
       <c r="C337" t="n">
-        <v>93.59</v>
+        <v>139.95</v>
       </c>
       <c r="D337" t="n">
-        <v>24256</v>
+        <v>18322</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>105.54</v>
+        <v>120.48</v>
       </c>
       <c r="B338" t="n">
-        <v>44756</v>
+        <v>19965</v>
       </c>
       <c r="C338" t="n">
-        <v>105.99</v>
+        <v>129.99</v>
       </c>
       <c r="D338" t="n">
-        <v>14218</v>
+        <v>14347</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>91.25</v>
+        <v>120.76</v>
       </c>
       <c r="B339" t="n">
-        <v>22872</v>
+        <v>21258</v>
       </c>
       <c r="C339" t="n">
-        <v>92.14</v>
+        <v>101.02</v>
       </c>
       <c r="D339" t="n">
-        <v>29355</v>
+        <v>27473</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>157.09</v>
+        <v>120.79</v>
       </c>
       <c r="B340" t="n">
-        <v>23295</v>
+        <v>21371</v>
       </c>
       <c r="C340" t="n">
-        <v>155.47</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="D340" t="n">
-        <v>23480</v>
+        <v>26425</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>91.91</v>
+        <v>121.02</v>
       </c>
       <c r="B341" t="n">
-        <v>26173</v>
+        <v>18707</v>
       </c>
       <c r="C341" t="n">
-        <v>94.93000000000001</v>
+        <v>103.89</v>
       </c>
       <c r="D341" t="n">
-        <v>26490</v>
+        <v>22422</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>94.65000000000001</v>
+        <v>121.11</v>
       </c>
       <c r="B342" t="n">
-        <v>33480</v>
+        <v>20315</v>
       </c>
       <c r="C342" t="n">
-        <v>95.55</v>
+        <v>104.04</v>
       </c>
       <c r="D342" t="n">
-        <v>19648</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>90.02</v>
+        <v>121.37</v>
       </c>
       <c r="B343" t="n">
-        <v>23805</v>
+        <v>20607</v>
       </c>
       <c r="C343" t="n">
-        <v>89.90000000000001</v>
+        <v>136.98</v>
       </c>
       <c r="D343" t="n">
-        <v>20082</v>
+        <v>13802</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>98.65000000000001</v>
+        <v>121.95</v>
       </c>
       <c r="B344" t="n">
-        <v>41639</v>
+        <v>19356</v>
       </c>
       <c r="C344" t="n">
-        <v>101.62</v>
+        <v>108.54</v>
       </c>
       <c r="D344" t="n">
-        <v>21877</v>
+        <v>23414</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>131.27</v>
+        <v>122.15</v>
       </c>
       <c r="B345" t="n">
-        <v>24499</v>
+        <v>21318</v>
       </c>
       <c r="C345" t="n">
-        <v>128.28</v>
+        <v>109.54</v>
       </c>
       <c r="D345" t="n">
-        <v>16562</v>
+        <v>13879</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>92.56</v>
+        <v>122.55</v>
       </c>
       <c r="B346" t="n">
-        <v>28711</v>
+        <v>18890</v>
       </c>
       <c r="C346" t="n">
-        <v>92.33</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="D346" t="n">
-        <v>17009</v>
+        <v>13066</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>174.74</v>
+        <v>122.75</v>
       </c>
       <c r="B347" t="n">
-        <v>22949</v>
+        <v>18602</v>
       </c>
       <c r="C347" t="n">
-        <v>179.55</v>
+        <v>126.87</v>
       </c>
       <c r="D347" t="n">
-        <v>17895</v>
+        <v>25714</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>101.69</v>
+        <v>123.6</v>
       </c>
       <c r="B348" t="n">
-        <v>48418</v>
+        <v>18003</v>
       </c>
       <c r="C348" t="n">
-        <v>102.29</v>
+        <v>144.8</v>
       </c>
       <c r="D348" t="n">
-        <v>23328</v>
+        <v>19862</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>91.3</v>
+        <v>124.18</v>
       </c>
       <c r="B349" t="n">
-        <v>24404</v>
+        <v>19364</v>
       </c>
       <c r="C349" t="n">
-        <v>92.7</v>
+        <v>119.76</v>
       </c>
       <c r="D349" t="n">
-        <v>15632</v>
+        <v>10071</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>96.70999999999999</v>
+        <v>125.49</v>
       </c>
       <c r="B350" t="n">
-        <v>37560</v>
+        <v>18156</v>
       </c>
       <c r="C350" t="n">
-        <v>97.22</v>
+        <v>137.7</v>
       </c>
       <c r="D350" t="n">
-        <v>23051</v>
+        <v>26684</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>106.98</v>
+        <v>126.08</v>
       </c>
       <c r="B351" t="n">
-        <v>42005</v>
+        <v>19134</v>
       </c>
       <c r="C351" t="n">
-        <v>109.69</v>
+        <v>107.85</v>
       </c>
       <c r="D351" t="n">
-        <v>27867</v>
+        <v>21196</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>107.3</v>
+        <v>126.31</v>
       </c>
       <c r="B352" t="n">
-        <v>41792</v>
+        <v>19316</v>
       </c>
       <c r="C352" t="n">
-        <v>104.02</v>
+        <v>138.49</v>
       </c>
       <c r="D352" t="n">
-        <v>13346</v>
+        <v>10382</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>112.08</v>
+        <v>126.8</v>
       </c>
       <c r="B353" t="n">
-        <v>27218</v>
+        <v>18448</v>
       </c>
       <c r="C353" t="n">
-        <v>115.56</v>
+        <v>140.03</v>
       </c>
       <c r="D353" t="n">
-        <v>15168</v>
+        <v>24965</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>92.78</v>
+        <v>127.54</v>
       </c>
       <c r="B354" t="n">
-        <v>25972</v>
+        <v>19940</v>
       </c>
       <c r="C354" t="n">
-        <v>93.84</v>
+        <v>143.29</v>
       </c>
       <c r="D354" t="n">
-        <v>17134</v>
+        <v>23742</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>102.45</v>
+        <v>127.86</v>
       </c>
       <c r="B355" t="n">
-        <v>47261</v>
+        <v>20675</v>
       </c>
       <c r="C355" t="n">
-        <v>97.91</v>
+        <v>122.66</v>
       </c>
       <c r="D355" t="n">
-        <v>27836</v>
+        <v>12219</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>96.98999999999999</v>
+        <v>127.93</v>
       </c>
       <c r="B356" t="n">
-        <v>40769</v>
+        <v>19683</v>
       </c>
       <c r="C356" t="n">
-        <v>98.09999999999999</v>
+        <v>141.96</v>
       </c>
       <c r="D356" t="n">
-        <v>11656</v>
+        <v>29278</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>100.11</v>
+        <v>129.04</v>
       </c>
       <c r="B357" t="n">
-        <v>41858</v>
+        <v>21098</v>
       </c>
       <c r="C357" t="n">
-        <v>101.65</v>
+        <v>135.39</v>
       </c>
       <c r="D357" t="n">
-        <v>24979</v>
+        <v>11125</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>101.73</v>
+        <v>129.39</v>
       </c>
       <c r="B358" t="n">
-        <v>46218</v>
+        <v>17995</v>
       </c>
       <c r="C358" t="n">
-        <v>98.56999999999999</v>
+        <v>148.91</v>
       </c>
       <c r="D358" t="n">
-        <v>13608</v>
+        <v>12465</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>98.51000000000001</v>
+        <v>129.7</v>
       </c>
       <c r="B359" t="n">
-        <v>42353</v>
+        <v>18840</v>
       </c>
       <c r="C359" t="n">
-        <v>101.27</v>
+        <v>142.74</v>
       </c>
       <c r="D359" t="n">
-        <v>11894</v>
+        <v>19427</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>175.28</v>
+        <v>130.41</v>
       </c>
       <c r="B360" t="n">
-        <v>22625</v>
+        <v>19973</v>
       </c>
       <c r="C360" t="n">
-        <v>168.72</v>
+        <v>108.08</v>
       </c>
       <c r="D360" t="n">
-        <v>29974</v>
+        <v>12985</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>93.06999999999999</v>
+        <v>130.58</v>
       </c>
       <c r="B361" t="n">
-        <v>26676</v>
+        <v>21142</v>
       </c>
       <c r="C361" t="n">
-        <v>95.55</v>
+        <v>134.73</v>
       </c>
       <c r="D361" t="n">
-        <v>19901</v>
+        <v>22860</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>110.37</v>
+        <v>130.63</v>
       </c>
       <c r="B362" t="n">
-        <v>32712</v>
+        <v>20171</v>
       </c>
       <c r="C362" t="n">
-        <v>110.83</v>
+        <v>108.71</v>
       </c>
       <c r="D362" t="n">
-        <v>13204</v>
+        <v>25230</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>90.77</v>
+        <v>131.2</v>
       </c>
       <c r="B363" t="n">
-        <v>23534</v>
+        <v>21541</v>
       </c>
       <c r="C363" t="n">
-        <v>92.75</v>
+        <v>154.85</v>
       </c>
       <c r="D363" t="n">
-        <v>26402</v>
+        <v>29824</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>99.86</v>
+        <v>131.28</v>
       </c>
       <c r="B364" t="n">
-        <v>43974</v>
+        <v>20486</v>
       </c>
       <c r="C364" t="n">
-        <v>102.39</v>
+        <v>149.2</v>
       </c>
       <c r="D364" t="n">
-        <v>16560</v>
+        <v>16412</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>47.77</v>
+        <v>131.4</v>
       </c>
       <c r="B365" t="n">
-        <v>23842</v>
+        <v>18248</v>
       </c>
       <c r="C365" t="n">
-        <v>46.08</v>
+        <v>119.22</v>
       </c>
       <c r="D365" t="n">
-        <v>24931</v>
+        <v>26637</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>88.73</v>
+        <v>131.47</v>
       </c>
       <c r="B366" t="n">
-        <v>24810</v>
+        <v>20117</v>
       </c>
       <c r="C366" t="n">
-        <v>91.78</v>
+        <v>135.38</v>
       </c>
       <c r="D366" t="n">
-        <v>19790</v>
+        <v>11857</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>96.76000000000001</v>
+        <v>131.52</v>
       </c>
       <c r="B367" t="n">
-        <v>37695</v>
+        <v>18853</v>
       </c>
       <c r="C367" t="n">
-        <v>98.28</v>
+        <v>121.96</v>
       </c>
       <c r="D367" t="n">
-        <v>23281</v>
+        <v>11283</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>98.73999999999999</v>
+        <v>131.69</v>
       </c>
       <c r="B368" t="n">
-        <v>42031</v>
+        <v>19896</v>
       </c>
       <c r="C368" t="n">
-        <v>96.90000000000001</v>
+        <v>120.12</v>
       </c>
       <c r="D368" t="n">
-        <v>20727</v>
+        <v>16750</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>91.66</v>
+        <v>132.41</v>
       </c>
       <c r="B369" t="n">
-        <v>25228</v>
+        <v>21037</v>
       </c>
       <c r="C369" t="n">
-        <v>91.09999999999999</v>
+        <v>141</v>
       </c>
       <c r="D369" t="n">
-        <v>21741</v>
+        <v>13681</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>91.33</v>
+        <v>132.64</v>
       </c>
       <c r="B370" t="n">
-        <v>24673</v>
+        <v>19918</v>
       </c>
       <c r="C370" t="n">
-        <v>90.73</v>
+        <v>150.44</v>
       </c>
       <c r="D370" t="n">
-        <v>21762</v>
+        <v>20812</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>104.85</v>
+        <v>133.83</v>
       </c>
       <c r="B371" t="n">
-        <v>47652</v>
+        <v>18870</v>
       </c>
       <c r="C371" t="n">
-        <v>105.73</v>
+        <v>157.41</v>
       </c>
       <c r="D371" t="n">
-        <v>22035</v>
+        <v>13740</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>97.3</v>
+        <v>134.54</v>
       </c>
       <c r="B372" t="n">
-        <v>37590</v>
+        <v>20098</v>
       </c>
       <c r="C372" t="n">
-        <v>94.25</v>
+        <v>152.13</v>
       </c>
       <c r="D372" t="n">
-        <v>10430</v>
+        <v>24076</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>94.20999999999999</v>
+        <v>135.37</v>
       </c>
       <c r="B373" t="n">
-        <v>29736</v>
+        <v>18171</v>
       </c>
       <c r="C373" t="n">
-        <v>91.01000000000001</v>
+        <v>116.34</v>
       </c>
       <c r="D373" t="n">
-        <v>15016</v>
+        <v>19041</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>92.73999999999999</v>
+        <v>135.52</v>
       </c>
       <c r="B374" t="n">
-        <v>26917</v>
+        <v>20863</v>
       </c>
       <c r="C374" t="n">
-        <v>91.77</v>
+        <v>128.71</v>
       </c>
       <c r="D374" t="n">
-        <v>25405</v>
+        <v>25252</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>110.42</v>
+        <v>135.8</v>
       </c>
       <c r="B375" t="n">
-        <v>31476</v>
+        <v>18888</v>
       </c>
       <c r="C375" t="n">
-        <v>107.07</v>
+        <v>109.24</v>
       </c>
       <c r="D375" t="n">
-        <v>12457</v>
+        <v>19408</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>101.67</v>
+        <v>135.87</v>
       </c>
       <c r="B376" t="n">
-        <v>48394</v>
+        <v>18958</v>
       </c>
       <c r="C376" t="n">
-        <v>98.29000000000001</v>
+        <v>123.24</v>
       </c>
       <c r="D376" t="n">
-        <v>28445</v>
+        <v>23642</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>96.11</v>
+        <v>136.13</v>
       </c>
       <c r="B377" t="n">
-        <v>37900</v>
+        <v>17880</v>
       </c>
       <c r="C377" t="n">
-        <v>93.42</v>
+        <v>139.59</v>
       </c>
       <c r="D377" t="n">
-        <v>21233</v>
+        <v>13185</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>87.66</v>
+        <v>136.57</v>
       </c>
       <c r="B378" t="n">
-        <v>21789</v>
+        <v>18919</v>
       </c>
       <c r="C378" t="n">
-        <v>89.56999999999999</v>
+        <v>151.62</v>
       </c>
       <c r="D378" t="n">
-        <v>14251</v>
+        <v>23169</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>96.86</v>
+        <v>136.57</v>
       </c>
       <c r="B379" t="n">
-        <v>39343</v>
+        <v>17509</v>
       </c>
       <c r="C379" t="n">
-        <v>95.69</v>
+        <v>164.02</v>
       </c>
       <c r="D379" t="n">
-        <v>21854</v>
+        <v>15815</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>102.85</v>
+        <v>137.7</v>
       </c>
       <c r="B380" t="n">
-        <v>44848</v>
+        <v>20645</v>
       </c>
       <c r="C380" t="n">
-        <v>107.35</v>
+        <v>157.44</v>
       </c>
       <c r="D380" t="n">
-        <v>25397</v>
+        <v>25975</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>82.73999999999999</v>
+        <v>137.77</v>
       </c>
       <c r="B381" t="n">
-        <v>22302</v>
+        <v>18706</v>
       </c>
       <c r="C381" t="n">
-        <v>81.03</v>
+        <v>170.99</v>
       </c>
       <c r="D381" t="n">
-        <v>27302</v>
+        <v>19508</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>104.4</v>
+        <v>137.96</v>
       </c>
       <c r="B382" t="n">
-        <v>48284</v>
+        <v>21071</v>
       </c>
       <c r="C382" t="n">
-        <v>104.86</v>
+        <v>139.37</v>
       </c>
       <c r="D382" t="n">
-        <v>11390</v>
+        <v>18627</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>152.02</v>
+        <v>138.1</v>
       </c>
       <c r="B383" t="n">
-        <v>23477</v>
+        <v>18796</v>
       </c>
       <c r="C383" t="n">
-        <v>148.31</v>
+        <v>103.23</v>
       </c>
       <c r="D383" t="n">
-        <v>23593</v>
+        <v>12721</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>112.2</v>
+        <v>138.12</v>
       </c>
       <c r="B384" t="n">
-        <v>26881</v>
+        <v>18474</v>
       </c>
       <c r="C384" t="n">
-        <v>115.62</v>
+        <v>123.48</v>
       </c>
       <c r="D384" t="n">
-        <v>13618</v>
+        <v>15110</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>106.34</v>
+        <v>138.75</v>
       </c>
       <c r="B385" t="n">
-        <v>42126</v>
+        <v>20451</v>
       </c>
       <c r="C385" t="n">
-        <v>108.51</v>
+        <v>130.01</v>
       </c>
       <c r="D385" t="n">
-        <v>21976</v>
+        <v>16565</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>55.79</v>
+        <v>139.68</v>
       </c>
       <c r="B386" t="n">
-        <v>21408</v>
+        <v>17581</v>
       </c>
       <c r="C386" t="n">
-        <v>53.88</v>
+        <v>146.47</v>
       </c>
       <c r="D386" t="n">
-        <v>19877</v>
+        <v>18372</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>91.17</v>
+        <v>140.02</v>
       </c>
       <c r="B387" t="n">
-        <v>26241</v>
+        <v>18965</v>
       </c>
       <c r="C387" t="n">
-        <v>93.92</v>
+        <v>139.12</v>
       </c>
       <c r="D387" t="n">
-        <v>17514</v>
+        <v>28633</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>95.29000000000001</v>
+        <v>140.32</v>
       </c>
       <c r="B388" t="n">
-        <v>34511</v>
+        <v>20981</v>
       </c>
       <c r="C388" t="n">
-        <v>96.20999999999999</v>
+        <v>161.96</v>
       </c>
       <c r="D388" t="n">
-        <v>25586</v>
+        <v>23999</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>99.76000000000001</v>
+        <v>140.54</v>
       </c>
       <c r="B389" t="n">
-        <v>43196</v>
+        <v>17395</v>
       </c>
       <c r="C389" t="n">
-        <v>96.93000000000001</v>
+        <v>152.26</v>
       </c>
       <c r="D389" t="n">
-        <v>27059</v>
+        <v>14882</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>97.84999999999999</v>
+        <v>140.63</v>
       </c>
       <c r="B390" t="n">
-        <v>42353</v>
+        <v>19402</v>
       </c>
       <c r="C390" t="n">
-        <v>98.68000000000001</v>
+        <v>155.58</v>
       </c>
       <c r="D390" t="n">
-        <v>28277</v>
+        <v>18364</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>76.56999999999999</v>
+        <v>140.86</v>
       </c>
       <c r="B391" t="n">
-        <v>23561</v>
+        <v>18336</v>
       </c>
       <c r="C391" t="n">
-        <v>78.41</v>
+        <v>120.8</v>
       </c>
       <c r="D391" t="n">
-        <v>21395</v>
+        <v>13103</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>100.87</v>
+        <v>141.3</v>
       </c>
       <c r="B392" t="n">
-        <v>47293</v>
+        <v>19112</v>
       </c>
       <c r="C392" t="n">
-        <v>100.96</v>
+        <v>149.03</v>
       </c>
       <c r="D392" t="n">
-        <v>25428</v>
+        <v>21471</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>102.95</v>
+        <v>142.42</v>
       </c>
       <c r="B393" t="n">
-        <v>44146</v>
+        <v>23822</v>
       </c>
       <c r="C393" t="n">
-        <v>100.55</v>
+        <v>152.24</v>
       </c>
       <c r="D393" t="n">
-        <v>21166</v>
+        <v>22638</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>103.52</v>
+        <v>142.82</v>
       </c>
       <c r="B394" t="n">
-        <v>44887</v>
+        <v>18127</v>
       </c>
       <c r="C394" t="n">
-        <v>101.59</v>
+        <v>165.87</v>
       </c>
       <c r="D394" t="n">
-        <v>19705</v>
+        <v>21476</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>96.54000000000001</v>
+        <v>142.89</v>
       </c>
       <c r="B395" t="n">
-        <v>37224</v>
+        <v>22367</v>
       </c>
       <c r="C395" t="n">
-        <v>95.45999999999999</v>
+        <v>130.63</v>
       </c>
       <c r="D395" t="n">
-        <v>13055</v>
+        <v>16954</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>109.08</v>
+        <v>143.08</v>
       </c>
       <c r="B396" t="n">
-        <v>34096</v>
+        <v>18743</v>
       </c>
       <c r="C396" t="n">
-        <v>109</v>
+        <v>139.13</v>
       </c>
       <c r="D396" t="n">
-        <v>22983</v>
+        <v>29486</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>100.05</v>
+        <v>143.64</v>
       </c>
       <c r="B397" t="n">
-        <v>43572</v>
+        <v>22270</v>
       </c>
       <c r="C397" t="n">
-        <v>101.38</v>
+        <v>147.5</v>
       </c>
       <c r="D397" t="n">
-        <v>29988</v>
+        <v>25879</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>98.70999999999999</v>
+        <v>144.12</v>
       </c>
       <c r="B398" t="n">
-        <v>42073</v>
+        <v>20252</v>
       </c>
       <c r="C398" t="n">
-        <v>98.97</v>
+        <v>137.48</v>
       </c>
       <c r="D398" t="n">
-        <v>27260</v>
+        <v>28051</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>106.92</v>
+        <v>144.16</v>
       </c>
       <c r="B399" t="n">
-        <v>40137</v>
+        <v>21607</v>
       </c>
       <c r="C399" t="n">
-        <v>109.7</v>
+        <v>120.82</v>
       </c>
       <c r="D399" t="n">
-        <v>18316</v>
+        <v>29038</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>98.88</v>
+        <v>144.28</v>
       </c>
       <c r="B400" t="n">
-        <v>42773</v>
+        <v>21565</v>
       </c>
       <c r="C400" t="n">
-        <v>100.56</v>
+        <v>146.12</v>
       </c>
       <c r="D400" t="n">
-        <v>16796</v>
+        <v>19277</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>107.51</v>
+        <v>144.37</v>
       </c>
       <c r="B401" t="n">
-        <v>39786</v>
+        <v>18150</v>
       </c>
       <c r="C401" t="n">
-        <v>107.54</v>
+        <v>154.07</v>
       </c>
       <c r="D401" t="n">
-        <v>10533</v>
+        <v>25220</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>112.01</v>
+        <v>145.63</v>
       </c>
       <c r="B402" t="n">
-        <v>28831</v>
+        <v>20126</v>
       </c>
       <c r="C402" t="n">
-        <v>111.67</v>
+        <v>165.87</v>
       </c>
       <c r="D402" t="n">
-        <v>15541</v>
+        <v>10277</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>23.42</v>
+        <v>145.68</v>
       </c>
       <c r="B403" t="n">
-        <v>22250</v>
+        <v>21130</v>
       </c>
       <c r="C403" t="n">
-        <v>24.2</v>
+        <v>165.45</v>
       </c>
       <c r="D403" t="n">
-        <v>23793</v>
+        <v>17114</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>96.89</v>
+        <v>146.23</v>
       </c>
       <c r="B404" t="n">
-        <v>37986</v>
+        <v>22205</v>
       </c>
       <c r="C404" t="n">
-        <v>98.69</v>
+        <v>142.42</v>
       </c>
       <c r="D404" t="n">
-        <v>23871</v>
+        <v>21618</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>103.55</v>
+        <v>146.43</v>
       </c>
       <c r="B405" t="n">
-        <v>46100</v>
+        <v>20381</v>
       </c>
       <c r="C405" t="n">
-        <v>102.8</v>
+        <v>172.35</v>
       </c>
       <c r="D405" t="n">
-        <v>23809</v>
+        <v>28991</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>93.16</v>
+        <v>146.98</v>
       </c>
       <c r="B406" t="n">
-        <v>29012</v>
+        <v>19881</v>
       </c>
       <c r="C406" t="n">
-        <v>95.75</v>
+        <v>132.27</v>
       </c>
       <c r="D406" t="n">
-        <v>13089</v>
+        <v>25913</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>109.91</v>
+        <v>147.06</v>
       </c>
       <c r="B407" t="n">
-        <v>37057</v>
+        <v>18662</v>
       </c>
       <c r="C407" t="n">
-        <v>105.77</v>
+        <v>137.22</v>
       </c>
       <c r="D407" t="n">
-        <v>15578</v>
+        <v>23389</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>109.26</v>
+        <v>147.23</v>
       </c>
       <c r="B408" t="n">
-        <v>34280</v>
+        <v>19283</v>
       </c>
       <c r="C408" t="n">
-        <v>108.25</v>
+        <v>129.08</v>
       </c>
       <c r="D408" t="n">
-        <v>18721</v>
+        <v>25107</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>90.23999999999999</v>
+        <v>147.65</v>
       </c>
       <c r="B409" t="n">
-        <v>23813</v>
+        <v>23021</v>
       </c>
       <c r="C409" t="n">
-        <v>89.25</v>
+        <v>117.24</v>
       </c>
       <c r="D409" t="n">
-        <v>13985</v>
+        <v>16823</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>112.39</v>
+        <v>147.97</v>
       </c>
       <c r="B410" t="n">
-        <v>26762</v>
+        <v>21591</v>
       </c>
       <c r="C410" t="n">
-        <v>109.14</v>
+        <v>158.02</v>
       </c>
       <c r="D410" t="n">
-        <v>12081</v>
+        <v>15300</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>102.33</v>
+        <v>148.03</v>
       </c>
       <c r="B411" t="n">
-        <v>46966</v>
+        <v>23352</v>
       </c>
       <c r="C411" t="n">
-        <v>98.33</v>
+        <v>179.14</v>
       </c>
       <c r="D411" t="n">
-        <v>17373</v>
+        <v>11993</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>112.34</v>
+        <v>148.48</v>
       </c>
       <c r="B412" t="n">
-        <v>26927</v>
+        <v>21309</v>
       </c>
       <c r="C412" t="n">
-        <v>111.17</v>
+        <v>137.64</v>
       </c>
       <c r="D412" t="n">
-        <v>16962</v>
+        <v>12272</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>6.7</v>
+        <v>148.74</v>
       </c>
       <c r="B413" t="n">
-        <v>24577</v>
+        <v>22356</v>
       </c>
       <c r="C413" t="n">
-        <v>7.09</v>
+        <v>120.77</v>
       </c>
       <c r="D413" t="n">
-        <v>11204</v>
+        <v>22810</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>53.92</v>
+        <v>148.86</v>
       </c>
       <c r="B414" t="n">
-        <v>24628</v>
+        <v>22117</v>
       </c>
       <c r="C414" t="n">
-        <v>54.73</v>
+        <v>119.08</v>
       </c>
       <c r="D414" t="n">
-        <v>16908</v>
+        <v>23731</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>99.12</v>
+        <v>149.17</v>
       </c>
       <c r="B415" t="n">
-        <v>43351</v>
+        <v>22195</v>
       </c>
       <c r="C415" t="n">
-        <v>96.33</v>
+        <v>121.83</v>
       </c>
       <c r="D415" t="n">
-        <v>25425</v>
+        <v>18203</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>105.81</v>
+        <v>149.43</v>
       </c>
       <c r="B416" t="n">
-        <v>47232</v>
+        <v>24611</v>
       </c>
       <c r="C416" t="n">
-        <v>107.71</v>
+        <v>180</v>
       </c>
       <c r="D416" t="n">
-        <v>20803</v>
+        <v>13236</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>12.65</v>
+        <v>150.63</v>
       </c>
       <c r="B417" t="n">
-        <v>24010</v>
+        <v>24696</v>
       </c>
       <c r="C417" t="n">
-        <v>12.13</v>
+        <v>180</v>
       </c>
       <c r="D417" t="n">
-        <v>25508</v>
+        <v>28055</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>34.05</v>
+        <v>150.63</v>
       </c>
       <c r="B418" t="n">
-        <v>23768</v>
+        <v>26012</v>
       </c>
       <c r="C418" t="n">
-        <v>34.5</v>
+        <v>160.41</v>
       </c>
       <c r="D418" t="n">
-        <v>12704</v>
+        <v>12762</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>110.01</v>
+        <v>150.85</v>
       </c>
       <c r="B419" t="n">
-        <v>32855</v>
+        <v>24980</v>
       </c>
       <c r="C419" t="n">
-        <v>108.2</v>
+        <v>132.16</v>
       </c>
       <c r="D419" t="n">
-        <v>27809</v>
+        <v>12318</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>97.92</v>
+        <v>151</v>
       </c>
       <c r="B420" t="n">
-        <v>41839</v>
+        <v>23306</v>
       </c>
       <c r="C420" t="n">
-        <v>94.36</v>
+        <v>135.08</v>
       </c>
       <c r="D420" t="n">
-        <v>23881</v>
+        <v>14106</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>84.09999999999999</v>
+        <v>151.04</v>
       </c>
       <c r="B421" t="n">
-        <v>21731</v>
+        <v>23900</v>
       </c>
       <c r="C421" t="n">
-        <v>86.63</v>
+        <v>124.69</v>
       </c>
       <c r="D421" t="n">
-        <v>24550</v>
+        <v>11423</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>99.95</v>
+        <v>151.62</v>
       </c>
       <c r="B422" t="n">
-        <v>43733</v>
+        <v>26873</v>
       </c>
       <c r="C422" t="n">
-        <v>100.85</v>
+        <v>168.68</v>
       </c>
       <c r="D422" t="n">
-        <v>22553</v>
+        <v>26787</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>114.84</v>
+        <v>151.7</v>
       </c>
       <c r="B423" t="n">
-        <v>22220</v>
+        <v>24158</v>
       </c>
       <c r="C423" t="n">
-        <v>119.33</v>
+        <v>140.86</v>
       </c>
       <c r="D423" t="n">
-        <v>21872</v>
+        <v>19107</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>109.42</v>
+        <v>151.84</v>
       </c>
       <c r="B424" t="n">
-        <v>36742</v>
+        <v>21608</v>
       </c>
       <c r="C424" t="n">
-        <v>109.08</v>
+        <v>180</v>
       </c>
       <c r="D424" t="n">
-        <v>28958</v>
+        <v>27052</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>100.81</v>
+        <v>152</v>
       </c>
       <c r="B425" t="n">
-        <v>46901</v>
+        <v>26065</v>
       </c>
       <c r="C425" t="n">
-        <v>103.48</v>
+        <v>180</v>
       </c>
       <c r="D425" t="n">
-        <v>12651</v>
+        <v>24858</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>102.46</v>
+        <v>152.11</v>
       </c>
       <c r="B426" t="n">
-        <v>45490</v>
+        <v>25799</v>
       </c>
       <c r="C426" t="n">
-        <v>101.38</v>
+        <v>158.87</v>
       </c>
       <c r="D426" t="n">
-        <v>18867</v>
+        <v>26072</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>75.61</v>
+        <v>153.07</v>
       </c>
       <c r="B427" t="n">
-        <v>21424</v>
+        <v>28209</v>
       </c>
       <c r="C427" t="n">
-        <v>76.15000000000001</v>
+        <v>149.98</v>
       </c>
       <c r="D427" t="n">
-        <v>25278</v>
+        <v>12835</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>91.19</v>
+        <v>153.32</v>
       </c>
       <c r="B428" t="n">
-        <v>23162</v>
+        <v>25478</v>
       </c>
       <c r="C428" t="n">
-        <v>89.16</v>
+        <v>131.95</v>
       </c>
       <c r="D428" t="n">
-        <v>21491</v>
+        <v>12182</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>48.03</v>
+        <v>153.4</v>
       </c>
       <c r="B429" t="n">
-        <v>23001</v>
+        <v>26317</v>
       </c>
       <c r="C429" t="n">
-        <v>48.43</v>
+        <v>177.72</v>
       </c>
       <c r="D429" t="n">
-        <v>11717</v>
+        <v>29762</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>106.42</v>
+        <v>153.56</v>
       </c>
       <c r="B430" t="n">
-        <v>43083</v>
+        <v>25481</v>
       </c>
       <c r="C430" t="n">
-        <v>105.59</v>
+        <v>148.37</v>
       </c>
       <c r="D430" t="n">
-        <v>22153</v>
+        <v>18804</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>95.68000000000001</v>
+        <v>153.6</v>
       </c>
       <c r="B431" t="n">
-        <v>38273</v>
+        <v>28361</v>
       </c>
       <c r="C431" t="n">
-        <v>94.2</v>
+        <v>179.95</v>
       </c>
       <c r="D431" t="n">
-        <v>28278</v>
+        <v>25480</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>56.05</v>
+        <v>153.73</v>
       </c>
       <c r="B432" t="n">
-        <v>22269</v>
+        <v>25031</v>
       </c>
       <c r="C432" t="n">
-        <v>55.04</v>
+        <v>167.76</v>
       </c>
       <c r="D432" t="n">
-        <v>21682</v>
+        <v>25267</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>96.91</v>
+        <v>154.2</v>
       </c>
       <c r="B433" t="n">
-        <v>38170</v>
+        <v>28159</v>
       </c>
       <c r="C433" t="n">
-        <v>98.84999999999999</v>
+        <v>148.18</v>
       </c>
       <c r="D433" t="n">
-        <v>24223</v>
+        <v>18855</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>104.06</v>
+        <v>154.22</v>
       </c>
       <c r="B434" t="n">
-        <v>47290</v>
+        <v>24116</v>
       </c>
       <c r="C434" t="n">
-        <v>107.98</v>
+        <v>125.9</v>
       </c>
       <c r="D434" t="n">
-        <v>21224</v>
+        <v>11295</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>175.2</v>
+        <v>154.35</v>
       </c>
       <c r="B435" t="n">
-        <v>22468</v>
+        <v>28800</v>
       </c>
       <c r="C435" t="n">
-        <v>170.74</v>
+        <v>160.66</v>
       </c>
       <c r="D435" t="n">
-        <v>20191</v>
+        <v>15725</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>105.98</v>
+        <v>154.45</v>
       </c>
       <c r="B436" t="n">
-        <v>43929</v>
+        <v>25959</v>
       </c>
       <c r="C436" t="n">
-        <v>109.22</v>
+        <v>133.14</v>
       </c>
       <c r="D436" t="n">
-        <v>25529</v>
+        <v>10845</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>167.05</v>
+        <v>154.54</v>
       </c>
       <c r="B437" t="n">
-        <v>25645</v>
+        <v>28412</v>
       </c>
       <c r="C437" t="n">
-        <v>163.63</v>
+        <v>136.59</v>
       </c>
       <c r="D437" t="n">
-        <v>22236</v>
+        <v>21071</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>93.95999999999999</v>
+        <v>155.05</v>
       </c>
       <c r="B438" t="n">
-        <v>28280</v>
+        <v>28754</v>
       </c>
       <c r="C438" t="n">
-        <v>95.52</v>
+        <v>139.59</v>
       </c>
       <c r="D438" t="n">
-        <v>18875</v>
+        <v>12552</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>93.34999999999999</v>
+        <v>155.25</v>
       </c>
       <c r="B439" t="n">
-        <v>27988</v>
+        <v>27912</v>
       </c>
       <c r="C439" t="n">
-        <v>94.31</v>
+        <v>125.01</v>
       </c>
       <c r="D439" t="n">
-        <v>10113</v>
+        <v>16549</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>155.32</v>
+        <v>155.6</v>
       </c>
       <c r="B440" t="n">
-        <v>24911</v>
+        <v>28807</v>
       </c>
       <c r="C440" t="n">
-        <v>152.98</v>
+        <v>151.16</v>
       </c>
       <c r="D440" t="n">
-        <v>13180</v>
+        <v>14963</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>105.69</v>
+        <v>155.77</v>
       </c>
       <c r="B441" t="n">
-        <v>44590</v>
+        <v>26675</v>
       </c>
       <c r="C441" t="n">
-        <v>107.86</v>
+        <v>176.79</v>
       </c>
       <c r="D441" t="n">
-        <v>18934</v>
+        <v>29855</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>113.16</v>
+        <v>156.61</v>
       </c>
       <c r="B442" t="n">
-        <v>25556</v>
+        <v>31062</v>
       </c>
       <c r="C442" t="n">
-        <v>112.22</v>
+        <v>174.85</v>
       </c>
       <c r="D442" t="n">
-        <v>21537</v>
+        <v>18589</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>109.26</v>
+        <v>156.61</v>
       </c>
       <c r="B443" t="n">
-        <v>33063</v>
+        <v>30571</v>
       </c>
       <c r="C443" t="n">
-        <v>107.58</v>
+        <v>166.85</v>
       </c>
       <c r="D443" t="n">
-        <v>11197</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>105.19</v>
+        <v>156.97</v>
       </c>
       <c r="B444" t="n">
-        <v>44818</v>
+        <v>28988</v>
       </c>
       <c r="C444" t="n">
-        <v>104.71</v>
+        <v>180</v>
       </c>
       <c r="D444" t="n">
-        <v>29874</v>
+        <v>20548</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>94.64</v>
+        <v>157.6</v>
       </c>
       <c r="B445" t="n">
-        <v>34294</v>
+        <v>31005</v>
       </c>
       <c r="C445" t="n">
-        <v>97.63</v>
+        <v>180</v>
       </c>
       <c r="D445" t="n">
-        <v>25648</v>
+        <v>26240</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>95.7</v>
+        <v>157.61</v>
       </c>
       <c r="B446" t="n">
-        <v>35149</v>
+        <v>29963</v>
       </c>
       <c r="C446" t="n">
-        <v>92.27</v>
+        <v>180</v>
       </c>
       <c r="D446" t="n">
-        <v>12844</v>
+        <v>12620</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>110.66</v>
+        <v>158.03</v>
       </c>
       <c r="B447" t="n">
-        <v>29782</v>
+        <v>29010</v>
       </c>
       <c r="C447" t="n">
-        <v>109.62</v>
+        <v>163.36</v>
       </c>
       <c r="D447" t="n">
-        <v>21881</v>
+        <v>11909</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>102.66</v>
+        <v>158.08</v>
       </c>
       <c r="B448" t="n">
-        <v>47977</v>
+        <v>30973</v>
       </c>
       <c r="C448" t="n">
-        <v>105.8</v>
+        <v>148.18</v>
       </c>
       <c r="D448" t="n">
-        <v>26658</v>
+        <v>26225</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>119.75</v>
+        <v>158.64</v>
       </c>
       <c r="B449" t="n">
-        <v>22536</v>
+        <v>30184</v>
       </c>
       <c r="C449" t="n">
-        <v>120.92</v>
+        <v>147.18</v>
       </c>
       <c r="D449" t="n">
-        <v>21450</v>
+        <v>29130</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>96.75</v>
+        <v>159.17</v>
       </c>
       <c r="B450" t="n">
-        <v>37254</v>
+        <v>33213</v>
       </c>
       <c r="C450" t="n">
-        <v>98.04000000000001</v>
+        <v>129.31</v>
       </c>
       <c r="D450" t="n">
-        <v>19571</v>
+        <v>26905</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>104.84</v>
+        <v>159.7</v>
       </c>
       <c r="B451" t="n">
-        <v>47034</v>
+        <v>32091</v>
       </c>
       <c r="C451" t="n">
-        <v>103.29</v>
+        <v>135.65</v>
       </c>
       <c r="D451" t="n">
-        <v>12268</v>
+        <v>20145</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>93.44</v>
+        <v>159.73</v>
       </c>
       <c r="B452" t="n">
-        <v>29416</v>
+        <v>30825</v>
       </c>
       <c r="C452" t="n">
-        <v>89.31999999999999</v>
+        <v>170.59</v>
       </c>
       <c r="D452" t="n">
-        <v>23254</v>
+        <v>12297</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>109.59</v>
+        <v>159.77</v>
       </c>
       <c r="B453" t="n">
-        <v>34880</v>
+        <v>32489</v>
       </c>
       <c r="C453" t="n">
-        <v>111.74</v>
+        <v>161.02</v>
       </c>
       <c r="D453" t="n">
-        <v>12573</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>95.64</v>
+        <v>159.77</v>
       </c>
       <c r="B454" t="n">
-        <v>36281</v>
+        <v>31975</v>
       </c>
       <c r="C454" t="n">
-        <v>96.84999999999999</v>
+        <v>155.18</v>
       </c>
       <c r="D454" t="n">
-        <v>28757</v>
+        <v>13107</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>112.01</v>
+        <v>160.33</v>
       </c>
       <c r="B455" t="n">
-        <v>26555</v>
+        <v>32265</v>
       </c>
       <c r="C455" t="n">
-        <v>111.24</v>
+        <v>167.49</v>
       </c>
       <c r="D455" t="n">
-        <v>18056</v>
+        <v>13391</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>101.77</v>
+        <v>160.46</v>
       </c>
       <c r="B456" t="n">
-        <v>44914</v>
+        <v>31243</v>
       </c>
       <c r="C456" t="n">
-        <v>100.26</v>
+        <v>166.84</v>
       </c>
       <c r="D456" t="n">
-        <v>24700</v>
+        <v>23734</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>108.58</v>
+        <v>160.79</v>
       </c>
       <c r="B457" t="n">
-        <v>34890</v>
+        <v>31859</v>
       </c>
       <c r="C457" t="n">
-        <v>106.35</v>
+        <v>131.7</v>
       </c>
       <c r="D457" t="n">
-        <v>20805</v>
+        <v>23175</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>108.39</v>
+        <v>162.04</v>
       </c>
       <c r="B458" t="n">
-        <v>37970</v>
+        <v>31978</v>
       </c>
       <c r="C458" t="n">
-        <v>110.43</v>
+        <v>180</v>
       </c>
       <c r="D458" t="n">
-        <v>18915</v>
+        <v>26416</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>96.5</v>
+        <v>162.6</v>
       </c>
       <c r="B459" t="n">
-        <v>39324</v>
+        <v>30706</v>
       </c>
       <c r="C459" t="n">
-        <v>94.06999999999999</v>
+        <v>143.34</v>
       </c>
       <c r="D459" t="n">
-        <v>15706</v>
+        <v>25109</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>100.97</v>
+        <v>163.29</v>
       </c>
       <c r="B460" t="n">
-        <v>45322</v>
+        <v>29895</v>
       </c>
       <c r="C460" t="n">
-        <v>104.8</v>
+        <v>146.07</v>
       </c>
       <c r="D460" t="n">
-        <v>28101</v>
+        <v>11009</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>104.2</v>
+        <v>163.87</v>
       </c>
       <c r="B461" t="n">
-        <v>46547</v>
+        <v>31248</v>
       </c>
       <c r="C461" t="n">
-        <v>101.16</v>
+        <v>133.21</v>
       </c>
       <c r="D461" t="n">
-        <v>16590</v>
+        <v>12324</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>15.66</v>
+        <v>164.57</v>
       </c>
       <c r="B462" t="n">
-        <v>24032</v>
+        <v>28441</v>
       </c>
       <c r="C462" t="n">
-        <v>16.63</v>
+        <v>152.08</v>
       </c>
       <c r="D462" t="n">
-        <v>12384</v>
+        <v>21025</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>90.28</v>
+        <v>164.76</v>
       </c>
       <c r="B463" t="n">
-        <v>23102</v>
+        <v>25407</v>
       </c>
       <c r="C463" t="n">
-        <v>94.22</v>
+        <v>165.64</v>
       </c>
       <c r="D463" t="n">
-        <v>27979</v>
+        <v>28989</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>95.09999999999999</v>
+        <v>166.35</v>
       </c>
       <c r="B464" t="n">
-        <v>34955</v>
+        <v>26927</v>
       </c>
       <c r="C464" t="n">
-        <v>95.91</v>
+        <v>139.36</v>
       </c>
       <c r="D464" t="n">
-        <v>27639</v>
+        <v>25994</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>97.77</v>
+        <v>166.44</v>
       </c>
       <c r="B465" t="n">
-        <v>41191</v>
+        <v>25978</v>
       </c>
       <c r="C465" t="n">
-        <v>99.88</v>
+        <v>180</v>
       </c>
       <c r="D465" t="n">
-        <v>18274</v>
+        <v>16404</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>142.23</v>
+        <v>166.51</v>
       </c>
       <c r="B466" t="n">
-        <v>23463</v>
+        <v>24987</v>
       </c>
       <c r="C466" t="n">
-        <v>139.15</v>
+        <v>166.21</v>
       </c>
       <c r="D466" t="n">
-        <v>14699</v>
+        <v>28310</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>107.63</v>
+        <v>166.99</v>
       </c>
       <c r="B467" t="n">
-        <v>41354</v>
+        <v>25805</v>
       </c>
       <c r="C467" t="n">
-        <v>107.62</v>
+        <v>180</v>
       </c>
       <c r="D467" t="n">
-        <v>28314</v>
+        <v>25064</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>102.58</v>
+        <v>167.04</v>
       </c>
       <c r="B468" t="n">
-        <v>44099</v>
+        <v>25134</v>
       </c>
       <c r="C468" t="n">
-        <v>101.59</v>
+        <v>139.88</v>
       </c>
       <c r="D468" t="n">
-        <v>29497</v>
+        <v>14493</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>101.76</v>
+        <v>167.17</v>
       </c>
       <c r="B469" t="n">
-        <v>45229</v>
+        <v>27196</v>
       </c>
       <c r="C469" t="n">
-        <v>103.88</v>
+        <v>180</v>
       </c>
       <c r="D469" t="n">
-        <v>11830</v>
+        <v>14923</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>70.05</v>
+        <v>167.78</v>
       </c>
       <c r="B470" t="n">
-        <v>22733</v>
+        <v>23623</v>
       </c>
       <c r="C470" t="n">
-        <v>72.88</v>
+        <v>180</v>
       </c>
       <c r="D470" t="n">
-        <v>13311</v>
+        <v>27255</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>106.19</v>
+        <v>168.3</v>
       </c>
       <c r="B471" t="n">
-        <v>44048</v>
+        <v>26512</v>
       </c>
       <c r="C471" t="n">
-        <v>109.24</v>
+        <v>180</v>
       </c>
       <c r="D471" t="n">
-        <v>28839</v>
+        <v>10527</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>22.66</v>
+        <v>168.85</v>
       </c>
       <c r="B472" t="n">
-        <v>24427</v>
+        <v>23305</v>
       </c>
       <c r="C472" t="n">
-        <v>23.51</v>
+        <v>180</v>
       </c>
       <c r="D472" t="n">
-        <v>20045</v>
+        <v>22455</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>97.36</v>
+        <v>169.56</v>
       </c>
       <c r="B473" t="n">
-        <v>40598</v>
+        <v>24216</v>
       </c>
       <c r="C473" t="n">
-        <v>101.44</v>
+        <v>143.84</v>
       </c>
       <c r="D473" t="n">
-        <v>29240</v>
+        <v>20602</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>108.7</v>
+        <v>170.61</v>
       </c>
       <c r="B474" t="n">
-        <v>37767</v>
+        <v>22600</v>
       </c>
       <c r="C474" t="n">
-        <v>110.25</v>
+        <v>167.6</v>
       </c>
       <c r="D474" t="n">
-        <v>19987</v>
+        <v>10561</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>137.86</v>
+        <v>170.64</v>
       </c>
       <c r="B475" t="n">
-        <v>22907</v>
+        <v>21048</v>
       </c>
       <c r="C475" t="n">
-        <v>136.75</v>
+        <v>180</v>
       </c>
       <c r="D475" t="n">
-        <v>21620</v>
+        <v>18646</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>107.67</v>
+        <v>171.65</v>
       </c>
       <c r="B476" t="n">
-        <v>40675</v>
+        <v>23856</v>
       </c>
       <c r="C476" t="n">
-        <v>108.61</v>
+        <v>138.16</v>
       </c>
       <c r="D476" t="n">
-        <v>10529</v>
+        <v>25687</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>100.83</v>
+        <v>171.92</v>
       </c>
       <c r="B477" t="n">
-        <v>47519</v>
+        <v>20701</v>
       </c>
       <c r="C477" t="n">
-        <v>100.46</v>
+        <v>173.47</v>
       </c>
       <c r="D477" t="n">
-        <v>19578</v>
+        <v>10596</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>107.29</v>
+        <v>172.03</v>
       </c>
       <c r="B478" t="n">
-        <v>40044</v>
+        <v>21701</v>
       </c>
       <c r="C478" t="n">
-        <v>109.31</v>
+        <v>171.74</v>
       </c>
       <c r="D478" t="n">
-        <v>27513</v>
+        <v>29101</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>93.94</v>
+        <v>172.99</v>
       </c>
       <c r="B479" t="n">
-        <v>29608</v>
+        <v>21317</v>
       </c>
       <c r="C479" t="n">
-        <v>92.2</v>
+        <v>142.17</v>
       </c>
       <c r="D479" t="n">
-        <v>23395</v>
+        <v>23758</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>93.25</v>
+        <v>173.63</v>
       </c>
       <c r="B480" t="n">
-        <v>26959</v>
+        <v>20745</v>
       </c>
       <c r="C480" t="n">
-        <v>91.83</v>
+        <v>171.19</v>
       </c>
       <c r="D480" t="n">
-        <v>23572</v>
+        <v>10424</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>92.02</v>
+        <v>173.83</v>
       </c>
       <c r="B481" t="n">
-        <v>24946</v>
+        <v>20378</v>
       </c>
       <c r="C481" t="n">
-        <v>94.70999999999999</v>
+        <v>180</v>
       </c>
       <c r="D481" t="n">
-        <v>15556</v>
+        <v>13695</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>105.41</v>
+        <v>173.92</v>
       </c>
       <c r="B482" t="n">
-        <v>43351</v>
+        <v>21340</v>
       </c>
       <c r="C482" t="n">
-        <v>106.34</v>
+        <v>180</v>
       </c>
       <c r="D482" t="n">
-        <v>22877</v>
+        <v>15215</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>1.28</v>
+        <v>174.55</v>
       </c>
       <c r="B483" t="n">
-        <v>25276</v>
+        <v>19420</v>
       </c>
       <c r="C483" t="n">
-        <v>0.42</v>
+        <v>180</v>
       </c>
       <c r="D483" t="n">
-        <v>25708</v>
+        <v>21095</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>103.49</v>
+        <v>174.67</v>
       </c>
       <c r="B484" t="n">
-        <v>48207</v>
+        <v>20524</v>
       </c>
       <c r="C484" t="n">
-        <v>100.64</v>
+        <v>169.01</v>
       </c>
       <c r="D484" t="n">
-        <v>22850</v>
+        <v>28913</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>105.69</v>
+        <v>174.67</v>
       </c>
       <c r="B485" t="n">
-        <v>46096</v>
+        <v>20222</v>
       </c>
       <c r="C485" t="n">
-        <v>108.42</v>
+        <v>175.31</v>
       </c>
       <c r="D485" t="n">
-        <v>26779</v>
+        <v>15932</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>38.19</v>
+        <v>175.39</v>
       </c>
       <c r="B486" t="n">
-        <v>20623</v>
+        <v>20056</v>
       </c>
       <c r="C486" t="n">
-        <v>37.33</v>
+        <v>180</v>
       </c>
       <c r="D486" t="n">
-        <v>29762</v>
+        <v>13561</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>94.5</v>
+        <v>175.48</v>
       </c>
       <c r="B487" t="n">
-        <v>30767</v>
+        <v>20426</v>
       </c>
       <c r="C487" t="n">
-        <v>93.47</v>
+        <v>156.29</v>
       </c>
       <c r="D487" t="n">
-        <v>25319</v>
+        <v>10189</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>114.96</v>
+        <v>176.44</v>
       </c>
       <c r="B488" t="n">
-        <v>25436</v>
+        <v>20388</v>
       </c>
       <c r="C488" t="n">
-        <v>115.36</v>
+        <v>157.51</v>
       </c>
       <c r="D488" t="n">
-        <v>29380</v>
+        <v>27171</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>110.4</v>
+        <v>177.39</v>
       </c>
       <c r="B489" t="n">
-        <v>32775</v>
+        <v>18839</v>
       </c>
       <c r="C489" t="n">
-        <v>108.22</v>
+        <v>142.73</v>
       </c>
       <c r="D489" t="n">
-        <v>16290</v>
+        <v>14358</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>97.04000000000001</v>
+        <v>177.58</v>
       </c>
       <c r="B490" t="n">
-        <v>37113</v>
+        <v>18729</v>
       </c>
       <c r="C490" t="n">
-        <v>98.84999999999999</v>
+        <v>162.6</v>
       </c>
       <c r="D490" t="n">
-        <v>21030</v>
+        <v>16233</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>109.17</v>
+        <v>178.57</v>
       </c>
       <c r="B491" t="n">
-        <v>35896</v>
+        <v>20061</v>
       </c>
       <c r="C491" t="n">
-        <v>107.7</v>
+        <v>180</v>
       </c>
       <c r="D491" t="n">
-        <v>15792</v>
+        <v>23365</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>108.33</v>
+        <v>178.58</v>
       </c>
       <c r="B492" t="n">
-        <v>37662</v>
+        <v>18220</v>
       </c>
       <c r="C492" t="n">
-        <v>104.44</v>
+        <v>180</v>
       </c>
       <c r="D492" t="n">
-        <v>19380</v>
+        <v>21030</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>103.31</v>
+        <v>178.64</v>
       </c>
       <c r="B493" t="n">
-        <v>49194</v>
+        <v>18685</v>
       </c>
       <c r="C493" t="n">
-        <v>104.58</v>
+        <v>180</v>
       </c>
       <c r="D493" t="n">
-        <v>28149</v>
+        <v>29272</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>94.66</v>
+        <v>178.8</v>
       </c>
       <c r="B494" t="n">
-        <v>30291</v>
+        <v>19446</v>
       </c>
       <c r="C494" t="n">
-        <v>97.03</v>
+        <v>180</v>
       </c>
       <c r="D494" t="n">
-        <v>13319</v>
+        <v>26175</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>92.90000000000001</v>
+        <v>178.84</v>
       </c>
       <c r="B495" t="n">
-        <v>26566</v>
+        <v>21133</v>
       </c>
       <c r="C495" t="n">
-        <v>90.27</v>
+        <v>168.51</v>
       </c>
       <c r="D495" t="n">
-        <v>26641</v>
+        <v>18474</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>95.55</v>
+        <v>178.99</v>
       </c>
       <c r="B496" t="n">
-        <v>34564</v>
+        <v>18386</v>
       </c>
       <c r="C496" t="n">
-        <v>97.93000000000001</v>
+        <v>149.19</v>
       </c>
       <c r="D496" t="n">
-        <v>21120</v>
+        <v>15247</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>155.47</v>
+        <v>179.03</v>
       </c>
       <c r="B497" t="n">
-        <v>24230</v>
+        <v>19030</v>
       </c>
       <c r="C497" t="n">
-        <v>152.89</v>
+        <v>164.47</v>
       </c>
       <c r="D497" t="n">
-        <v>27432</v>
+        <v>27869</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>96.76000000000001</v>
+        <v>179.79</v>
       </c>
       <c r="B498" t="n">
-        <v>37880</v>
+        <v>18212</v>
       </c>
       <c r="C498" t="n">
-        <v>98.81999999999999</v>
+        <v>148.34</v>
       </c>
       <c r="D498" t="n">
-        <v>23251</v>
+        <v>19124</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>93.63</v>
+        <v>179.8</v>
       </c>
       <c r="B499" t="n">
-        <v>28315</v>
+        <v>17879</v>
       </c>
       <c r="C499" t="n">
-        <v>95.81999999999999</v>
+        <v>180</v>
       </c>
       <c r="D499" t="n">
-        <v>17422</v>
+        <v>19877</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>112.57</v>
+        <v>179.91</v>
       </c>
       <c r="B500" t="n">
-        <v>24806</v>
+        <v>19384</v>
       </c>
       <c r="C500" t="n">
-        <v>111.92</v>
+        <v>180</v>
       </c>
       <c r="D500" t="n">
-        <v>13344</v>
+        <v>15813</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>93.77</v>
+        <v>179.93</v>
       </c>
       <c r="B501" t="n">
-        <v>29848</v>
+        <v>20343</v>
       </c>
       <c r="C501" t="n">
-        <v>93.43000000000001</v>
+        <v>180</v>
       </c>
       <c r="D501" t="n">
-        <v>21233</v>
+        <v>15074</v>
       </c>
     </row>
   </sheetData>
